--- a/research/traditional_assets/database/data/oman/oman_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_telecom_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08667580553052057</v>
+        <v>0.08658404182222479</v>
       </c>
       <c r="C2">
-        <v>10149.652660896</v>
+        <v>10060.63355232527</v>
       </c>
       <c r="D2">
-        <v>9325.952660895999</v>
+        <v>9331.957552325264</v>
       </c>
       <c r="E2">
-        <v>-7671.6</v>
+        <v>-7576.576</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>95.024</v>
       </c>
       <c r="G2">
         <v>823.7</v>
@@ -1451,28 +1451,28 @@
         <v>1573.55</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.7797072</v>
       </c>
       <c r="N2">
-        <v>1573.55</v>
+        <v>1568.7702928</v>
       </c>
       <c r="O2">
-        <v>236.0325</v>
+        <v>235.31554392</v>
       </c>
       <c r="P2">
-        <v>1337.5175</v>
+        <v>1333.45474888</v>
       </c>
       <c r="Q2">
-        <v>2882.7175</v>
+        <v>2878.65474888</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08667580553052057</v>
+        <v>0.08702675941638868</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.537322879721409</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>329.2147267933065</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08658404182222479</v>
+        <v>0.08649227811392901</v>
       </c>
       <c r="C3">
-        <v>10060.63355232527</v>
+        <v>9971.622181720872</v>
       </c>
       <c r="D3">
-        <v>9331.957552325264</v>
+        <v>9337.970181720872</v>
       </c>
       <c r="E3">
-        <v>-7576.576</v>
+        <v>-7481.552000000001</v>
       </c>
       <c r="F3">
-        <v>95.024</v>
+        <v>190.048</v>
       </c>
       <c r="G3">
         <v>823.7</v>
@@ -1533,28 +1533,28 @@
         <v>1573.55</v>
       </c>
       <c r="M3">
-        <v>4.7797072</v>
+        <v>9.5594144</v>
       </c>
       <c r="N3">
-        <v>1568.7702928</v>
+        <v>1563.9905856</v>
       </c>
       <c r="O3">
-        <v>235.31554392</v>
+        <v>234.59858784</v>
       </c>
       <c r="P3">
-        <v>1333.45474888</v>
+        <v>1329.39199776</v>
       </c>
       <c r="Q3">
-        <v>2878.65474888</v>
+        <v>2874.59199776</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08702675941638868</v>
+        <v>0.08738487562645818</v>
       </c>
       <c r="T3">
-        <v>0.537322879721409</v>
+        <v>0.5419903344521092</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>329.2147267933065</v>
+        <v>164.6073633966533</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08649227811392901</v>
+        <v>0.08640051440563322</v>
       </c>
       <c r="C4">
-        <v>9971.622181720872</v>
+        <v>9882.618564049306</v>
       </c>
       <c r="D4">
-        <v>9337.970181720872</v>
+        <v>9343.990564049305</v>
       </c>
       <c r="E4">
-        <v>-7481.552000000001</v>
+        <v>-7386.528</v>
       </c>
       <c r="F4">
-        <v>190.048</v>
+        <v>285.072</v>
       </c>
       <c r="G4">
         <v>823.7</v>
@@ -1615,28 +1615,28 @@
         <v>1573.55</v>
       </c>
       <c r="M4">
-        <v>9.5594144</v>
+        <v>14.3391216</v>
       </c>
       <c r="N4">
-        <v>1563.9905856</v>
+        <v>1559.2108784</v>
       </c>
       <c r="O4">
-        <v>234.59858784</v>
+        <v>233.88163176</v>
       </c>
       <c r="P4">
-        <v>1329.39199776</v>
+        <v>1325.32924664</v>
       </c>
       <c r="Q4">
-        <v>2874.59199776</v>
+        <v>2870.52924664</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08738487562645818</v>
+        <v>0.08775037567591054</v>
       </c>
       <c r="T4">
-        <v>0.5419903344521092</v>
+        <v>0.5467540253628237</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>164.6073633966533</v>
+        <v>109.7382422644355</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08640051440563322</v>
+        <v>0.08630875069733744</v>
       </c>
       <c r="C5">
-        <v>9882.618564049306</v>
+        <v>9793.622714315663</v>
       </c>
       <c r="D5">
-        <v>9343.990564049305</v>
+        <v>9350.018714315662</v>
       </c>
       <c r="E5">
-        <v>-7386.528</v>
+        <v>-7291.504000000001</v>
       </c>
       <c r="F5">
-        <v>285.072</v>
+        <v>380.096</v>
       </c>
       <c r="G5">
         <v>823.7</v>
@@ -1697,28 +1697,28 @@
         <v>1573.55</v>
       </c>
       <c r="M5">
-        <v>14.3391216</v>
+        <v>19.1188288</v>
       </c>
       <c r="N5">
-        <v>1559.2108784</v>
+        <v>1554.4311712</v>
       </c>
       <c r="O5">
-        <v>233.88163176</v>
+        <v>233.16467568</v>
       </c>
       <c r="P5">
-        <v>1325.32924664</v>
+        <v>1321.26649552</v>
       </c>
       <c r="Q5">
-        <v>2870.52924664</v>
+        <v>2866.46649552</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08775037567591054</v>
+        <v>0.08812349030972651</v>
       </c>
       <c r="T5">
-        <v>0.5467540253628237</v>
+        <v>0.5516169598341781</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>109.7382422644355</v>
+        <v>82.30368169832663</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08630875069733744</v>
+        <v>0.08621698698904165</v>
       </c>
       <c r="C6">
-        <v>9793.622714315663</v>
+        <v>9704.634647563791</v>
       </c>
       <c r="D6">
-        <v>9350.018714315662</v>
+        <v>9356.054647563791</v>
       </c>
       <c r="E6">
-        <v>-7291.504000000001</v>
+        <v>-7196.48</v>
       </c>
       <c r="F6">
-        <v>380.096</v>
+        <v>475.12</v>
       </c>
       <c r="G6">
         <v>823.7</v>
@@ -1779,28 +1779,28 @@
         <v>1573.55</v>
       </c>
       <c r="M6">
-        <v>19.1188288</v>
+        <v>23.898536</v>
       </c>
       <c r="N6">
-        <v>1554.4311712</v>
+        <v>1549.651464</v>
       </c>
       <c r="O6">
-        <v>233.16467568</v>
+        <v>232.4477196</v>
       </c>
       <c r="P6">
-        <v>1321.26649552</v>
+        <v>1317.2037444</v>
       </c>
       <c r="Q6">
-        <v>2866.46649552</v>
+        <v>2862.4037444</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08812349030972651</v>
+        <v>0.0885044599884649</v>
       </c>
       <c r="T6">
-        <v>0.5516169598341781</v>
+        <v>0.5565822718733505</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>82.30368169832663</v>
+        <v>65.8429453586613</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08621698698904165</v>
+        <v>0.08612522328074589</v>
       </c>
       <c r="C7">
-        <v>9704.634647563791</v>
+        <v>9615.654378876412</v>
       </c>
       <c r="D7">
-        <v>9356.054647563791</v>
+        <v>9362.098378876412</v>
       </c>
       <c r="E7">
-        <v>-7196.48</v>
+        <v>-7101.456</v>
       </c>
       <c r="F7">
-        <v>475.12</v>
+        <v>570.144</v>
       </c>
       <c r="G7">
         <v>823.7</v>
@@ -1861,28 +1861,28 @@
         <v>1573.55</v>
       </c>
       <c r="M7">
-        <v>23.898536</v>
+        <v>28.6782432</v>
       </c>
       <c r="N7">
-        <v>1549.651464</v>
+        <v>1544.8717568</v>
       </c>
       <c r="O7">
-        <v>232.4477196</v>
+        <v>231.73076352</v>
       </c>
       <c r="P7">
-        <v>1317.2037444</v>
+        <v>1313.14099328</v>
       </c>
       <c r="Q7">
-        <v>2862.4037444</v>
+        <v>2858.34099328</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0885044599884649</v>
+        <v>0.08889353540504881</v>
       </c>
       <c r="T7">
-        <v>0.5565822718733505</v>
+        <v>0.5616532288495266</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>65.8429453586613</v>
+        <v>54.86912113221776</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08612522328074587</v>
+        <v>0.08603345957245011</v>
       </c>
       <c r="C8">
-        <v>9615.654378876414</v>
+        <v>9526.681923375247</v>
       </c>
       <c r="D8">
-        <v>9362.098378876413</v>
+        <v>9368.149923375246</v>
       </c>
       <c r="E8">
-        <v>-7101.456</v>
+        <v>-7006.432000000001</v>
       </c>
       <c r="F8">
-        <v>570.144</v>
+        <v>665.1679999999999</v>
       </c>
       <c r="G8">
         <v>823.7</v>
@@ -1943,28 +1943,28 @@
         <v>1573.55</v>
       </c>
       <c r="M8">
-        <v>28.6782432</v>
+        <v>33.45795039999999</v>
       </c>
       <c r="N8">
-        <v>1544.8717568</v>
+        <v>1540.0920496</v>
       </c>
       <c r="O8">
-        <v>231.73076352</v>
+        <v>231.01380744</v>
       </c>
       <c r="P8">
-        <v>1313.14099328</v>
+        <v>1309.07824216</v>
       </c>
       <c r="Q8">
-        <v>2858.34099328</v>
+        <v>2854.27824216</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08889353540504881</v>
+        <v>0.08929097803489258</v>
       </c>
       <c r="T8">
-        <v>0.5616532288495266</v>
+        <v>0.5668332386639</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>54.86912113221776</v>
+        <v>47.03067525618665</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08603345957245009</v>
+        <v>0.08594169586415433</v>
       </c>
       <c r="C9">
-        <v>9526.681923375249</v>
+        <v>9437.71729622113</v>
       </c>
       <c r="D9">
-        <v>9368.149923375247</v>
+        <v>9374.209296221128</v>
       </c>
       <c r="E9">
-        <v>-7006.432000000001</v>
+        <v>-6911.408</v>
       </c>
       <c r="F9">
-        <v>665.168</v>
+        <v>760.192</v>
       </c>
       <c r="G9">
         <v>823.7</v>
@@ -2025,28 +2025,28 @@
         <v>1573.55</v>
       </c>
       <c r="M9">
-        <v>33.4579504</v>
+        <v>38.2376576</v>
       </c>
       <c r="N9">
-        <v>1540.0920496</v>
+        <v>1535.3123424</v>
       </c>
       <c r="O9">
-        <v>231.01380744</v>
+        <v>230.29685136</v>
       </c>
       <c r="P9">
-        <v>1309.07824216</v>
+        <v>1305.01549104</v>
       </c>
       <c r="Q9">
-        <v>2854.27824216</v>
+        <v>2850.21549104</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08929097803489258</v>
+        <v>0.08969706072190688</v>
       </c>
       <c r="T9">
-        <v>0.5668332386639</v>
+        <v>0.5721258573872816</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>47.03067525618664</v>
+        <v>41.15184084916331</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08594169586415433</v>
+        <v>0.08584993215585854</v>
       </c>
       <c r="C10">
-        <v>9437.71729622113</v>
+        <v>9348.760512614155</v>
       </c>
       <c r="D10">
-        <v>9374.209296221128</v>
+        <v>9380.276512614155</v>
       </c>
       <c r="E10">
-        <v>-6911.408</v>
+        <v>-6816.384</v>
       </c>
       <c r="F10">
-        <v>760.192</v>
+        <v>855.2159999999999</v>
       </c>
       <c r="G10">
         <v>823.7</v>
@@ -2107,28 +2107,28 @@
         <v>1573.55</v>
       </c>
       <c r="M10">
-        <v>38.2376576</v>
+        <v>43.0173648</v>
       </c>
       <c r="N10">
-        <v>1535.3123424</v>
+        <v>1530.5326352</v>
       </c>
       <c r="O10">
-        <v>230.29685136</v>
+        <v>229.57989528</v>
       </c>
       <c r="P10">
-        <v>1305.01549104</v>
+        <v>1300.95273992</v>
       </c>
       <c r="Q10">
-        <v>2850.21549104</v>
+        <v>2846.15273992</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08969706072190688</v>
+        <v>0.09011206830314125</v>
       </c>
       <c r="T10">
-        <v>0.5721258573872816</v>
+        <v>0.5775347974012869</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>41.15184084916331</v>
+        <v>36.57941408814517</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08584993215585854</v>
+        <v>0.08575816844756276</v>
       </c>
       <c r="C11">
-        <v>9348.760512614155</v>
+        <v>9259.811587793791</v>
       </c>
       <c r="D11">
-        <v>9380.276512614155</v>
+        <v>9386.35158779379</v>
       </c>
       <c r="E11">
-        <v>-6816.384</v>
+        <v>-6721.360000000001</v>
       </c>
       <c r="F11">
-        <v>855.2159999999999</v>
+        <v>950.2399999999999</v>
       </c>
       <c r="G11">
         <v>823.7</v>
@@ -2189,28 +2189,28 @@
         <v>1573.55</v>
       </c>
       <c r="M11">
-        <v>43.0173648</v>
+        <v>47.79707199999999</v>
       </c>
       <c r="N11">
-        <v>1530.5326352</v>
+        <v>1525.752928</v>
       </c>
       <c r="O11">
-        <v>229.57989528</v>
+        <v>228.8629392</v>
       </c>
       <c r="P11">
-        <v>1300.95273992</v>
+        <v>1296.8899888</v>
       </c>
       <c r="Q11">
-        <v>2846.15273992</v>
+        <v>2842.0899888</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09011206830314125</v>
+        <v>0.09053629827506973</v>
       </c>
       <c r="T11">
-        <v>0.5775347974012869</v>
+        <v>0.5830639360822701</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>36.57941408814517</v>
+        <v>32.92147267933065</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08575816844756276</v>
+        <v>0.08566640473926698</v>
       </c>
       <c r="C12">
-        <v>9259.811587793791</v>
+        <v>9170.870537039003</v>
       </c>
       <c r="D12">
-        <v>9386.35158779379</v>
+        <v>9392.434537039002</v>
       </c>
       <c r="E12">
-        <v>-6721.360000000001</v>
+        <v>-6626.336</v>
       </c>
       <c r="F12">
-        <v>950.24</v>
+        <v>1045.264</v>
       </c>
       <c r="G12">
         <v>823.7</v>
@@ -2271,28 +2271,28 @@
         <v>1573.55</v>
       </c>
       <c r="M12">
-        <v>47.797072</v>
+        <v>52.57677919999999</v>
       </c>
       <c r="N12">
-        <v>1525.752928</v>
+        <v>1520.9732208</v>
       </c>
       <c r="O12">
-        <v>228.8629392</v>
+        <v>228.14598312</v>
       </c>
       <c r="P12">
-        <v>1296.8899888</v>
+        <v>1292.82723768</v>
       </c>
       <c r="Q12">
-        <v>2842.0899888</v>
+        <v>2838.02723768</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09053629827506973</v>
+        <v>0.09097006150479436</v>
       </c>
       <c r="T12">
-        <v>0.5830639360822701</v>
+        <v>0.5887173250706912</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>32.92147267933065</v>
+        <v>29.92861152666423</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08566640473926698</v>
+        <v>0.0855746410309712</v>
       </c>
       <c r="C13">
-        <v>9170.870537039003</v>
+        <v>9081.9373756684</v>
       </c>
       <c r="D13">
-        <v>9392.434537039002</v>
+        <v>9398.5253756684</v>
       </c>
       <c r="E13">
-        <v>-6626.336</v>
+        <v>-6531.312</v>
       </c>
       <c r="F13">
-        <v>1045.264</v>
+        <v>1140.288</v>
       </c>
       <c r="G13">
         <v>823.7</v>
@@ -2353,28 +2353,28 @@
         <v>1573.55</v>
       </c>
       <c r="M13">
-        <v>52.57677919999999</v>
+        <v>57.35648639999999</v>
       </c>
       <c r="N13">
-        <v>1520.9732208</v>
+        <v>1516.1935136</v>
       </c>
       <c r="O13">
-        <v>228.14598312</v>
+        <v>227.42902704</v>
       </c>
       <c r="P13">
-        <v>1292.82723768</v>
+        <v>1288.76448656</v>
       </c>
       <c r="Q13">
-        <v>2838.02723768</v>
+        <v>2833.96448656</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09097006150479436</v>
+        <v>0.09141368298974001</v>
       </c>
       <c r="T13">
-        <v>0.5887173250706912</v>
+        <v>0.5944992001724854</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>29.92861152666423</v>
+        <v>27.43456056610888</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0855746410309712</v>
+        <v>0.08548287732267541</v>
       </c>
       <c r="C14">
-        <v>9081.9373756684</v>
+        <v>8993.012119040348</v>
       </c>
       <c r="D14">
-        <v>9398.5253756684</v>
+        <v>9404.624119040347</v>
       </c>
       <c r="E14">
-        <v>-6531.312</v>
+        <v>-6436.288</v>
       </c>
       <c r="F14">
-        <v>1140.288</v>
+        <v>1235.312</v>
       </c>
       <c r="G14">
         <v>823.7</v>
@@ -2435,28 +2435,28 @@
         <v>1573.55</v>
       </c>
       <c r="M14">
-        <v>57.35648639999999</v>
+        <v>62.13619359999999</v>
       </c>
       <c r="N14">
-        <v>1516.1935136</v>
+        <v>1511.4138064</v>
       </c>
       <c r="O14">
-        <v>227.42902704</v>
+        <v>226.71207096</v>
       </c>
       <c r="P14">
-        <v>1288.76448656</v>
+        <v>1284.70173544</v>
       </c>
       <c r="Q14">
-        <v>2833.96448656</v>
+        <v>2829.90173544</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09141368298974001</v>
+        <v>0.09186750266974186</v>
       </c>
       <c r="T14">
-        <v>0.5944992001724854</v>
+        <v>0.6004139919432864</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>27.43456056610888</v>
+        <v>25.32420975333127</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08548287732267541</v>
+        <v>0.08539111361437962</v>
       </c>
       <c r="C15">
-        <v>8993.012119040348</v>
+        <v>8904.094782553102</v>
       </c>
       <c r="D15">
-        <v>9404.624119040347</v>
+        <v>9410.730782553101</v>
       </c>
       <c r="E15">
-        <v>-6436.288</v>
+        <v>-6341.264</v>
       </c>
       <c r="F15">
-        <v>1235.312</v>
+        <v>1330.336</v>
       </c>
       <c r="G15">
         <v>823.7</v>
@@ -2517,28 +2517,28 @@
         <v>1573.55</v>
       </c>
       <c r="M15">
-        <v>62.13619359999999</v>
+        <v>66.9159008</v>
       </c>
       <c r="N15">
-        <v>1511.4138064</v>
+        <v>1506.6340992</v>
       </c>
       <c r="O15">
-        <v>226.71207096</v>
+        <v>225.99511488</v>
       </c>
       <c r="P15">
-        <v>1284.70173544</v>
+        <v>1280.63898432</v>
       </c>
       <c r="Q15">
-        <v>2829.90173544</v>
+        <v>2825.83898432</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09186750266974186</v>
+        <v>0.09233187629579026</v>
       </c>
       <c r="T15">
-        <v>0.6004139919432864</v>
+        <v>0.6064663370110827</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>25.32420975333127</v>
+        <v>23.51533762809332</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08539111361437962</v>
+        <v>0.08529934990608384</v>
       </c>
       <c r="C16">
-        <v>8904.094782553102</v>
+        <v>8815.185381644933</v>
       </c>
       <c r="D16">
-        <v>9410.730782553101</v>
+        <v>9416.845381644933</v>
       </c>
       <c r="E16">
-        <v>-6341.264</v>
+        <v>-6246.24</v>
       </c>
       <c r="F16">
-        <v>1330.336</v>
+        <v>1425.36</v>
       </c>
       <c r="G16">
         <v>823.7</v>
@@ -2599,28 +2599,28 @@
         <v>1573.55</v>
       </c>
       <c r="M16">
-        <v>66.9159008</v>
+        <v>71.69560800000001</v>
       </c>
       <c r="N16">
-        <v>1506.6340992</v>
+        <v>1501.854392</v>
       </c>
       <c r="O16">
-        <v>225.99511488</v>
+        <v>225.2781588</v>
       </c>
       <c r="P16">
-        <v>1280.63898432</v>
+        <v>1276.5762332</v>
       </c>
       <c r="Q16">
-        <v>2825.83898432</v>
+        <v>2821.7762332</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09233187629579026</v>
+        <v>0.09280717636009865</v>
       </c>
       <c r="T16">
-        <v>0.6064663370110827</v>
+        <v>0.6126610901981213</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>23.51533762809332</v>
+        <v>21.9476484528871</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08529934990608384</v>
+        <v>0.08520758619778807</v>
       </c>
       <c r="C17">
-        <v>8815.185381644933</v>
+        <v>8726.283931794274</v>
       </c>
       <c r="D17">
-        <v>9416.845381644933</v>
+        <v>9422.967931794274</v>
       </c>
       <c r="E17">
-        <v>-6246.240000000001</v>
+        <v>-6151.216</v>
       </c>
       <c r="F17">
-        <v>1425.36</v>
+        <v>1520.384</v>
       </c>
       <c r="G17">
         <v>823.7</v>
@@ -2681,28 +2681,28 @@
         <v>1573.55</v>
       </c>
       <c r="M17">
-        <v>71.69560799999999</v>
+        <v>76.4753152</v>
       </c>
       <c r="N17">
-        <v>1501.854392</v>
+        <v>1497.0746848</v>
       </c>
       <c r="O17">
-        <v>225.2781588</v>
+        <v>224.56120272</v>
       </c>
       <c r="P17">
-        <v>1276.5762332</v>
+        <v>1272.51348208</v>
       </c>
       <c r="Q17">
-        <v>2821.7762332</v>
+        <v>2817.71348208</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09280717636009865</v>
+        <v>0.09329379309260485</v>
       </c>
       <c r="T17">
-        <v>0.6126610901981213</v>
+        <v>0.619003337508661</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.9476484528871</v>
+        <v>20.57592042458166</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08520758619778807</v>
+        <v>0.08511582248949229</v>
       </c>
       <c r="C18">
-        <v>8726.283931794274</v>
+        <v>8637.390448519829</v>
       </c>
       <c r="D18">
-        <v>9422.967931794274</v>
+        <v>9429.098448519828</v>
       </c>
       <c r="E18">
-        <v>-6151.216</v>
+        <v>-6056.192</v>
       </c>
       <c r="F18">
-        <v>1520.384</v>
+        <v>1615.408</v>
       </c>
       <c r="G18">
         <v>823.7</v>
@@ -2763,28 +2763,28 @@
         <v>1573.55</v>
       </c>
       <c r="M18">
-        <v>76.4753152</v>
+        <v>81.2550224</v>
       </c>
       <c r="N18">
-        <v>1497.0746848</v>
+        <v>1492.2949776</v>
       </c>
       <c r="O18">
-        <v>224.56120272</v>
+        <v>223.84424664</v>
       </c>
       <c r="P18">
-        <v>1272.51348208</v>
+        <v>1268.45073096</v>
       </c>
       <c r="Q18">
-        <v>2817.71348208</v>
+        <v>2813.65073096</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09329379309260485</v>
+        <v>0.0937921355295088</v>
       </c>
       <c r="T18">
-        <v>0.619003337508661</v>
+        <v>0.625498410055599</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.57592042458166</v>
+        <v>19.36557216431215</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08511582248949229</v>
+        <v>0.08502405878119651</v>
       </c>
       <c r="C19">
-        <v>8637.390448519829</v>
+        <v>8548.504947380714</v>
       </c>
       <c r="D19">
-        <v>9429.098448519828</v>
+        <v>9435.236947380714</v>
       </c>
       <c r="E19">
-        <v>-6056.192</v>
+        <v>-5961.168</v>
       </c>
       <c r="F19">
-        <v>1615.408</v>
+        <v>1710.432</v>
       </c>
       <c r="G19">
         <v>823.7</v>
@@ -2845,28 +2845,28 @@
         <v>1573.55</v>
       </c>
       <c r="M19">
-        <v>81.2550224</v>
+        <v>86.03472960000001</v>
       </c>
       <c r="N19">
-        <v>1492.2949776</v>
+        <v>1487.5152704</v>
       </c>
       <c r="O19">
-        <v>223.84424664</v>
+        <v>223.12729056</v>
       </c>
       <c r="P19">
-        <v>1268.45073096</v>
+        <v>1264.38797984</v>
       </c>
       <c r="Q19">
-        <v>2813.65073096</v>
+        <v>2809.58797984</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0937921355295088</v>
+        <v>0.09430263265999575</v>
       </c>
       <c r="T19">
-        <v>0.625498410055599</v>
+        <v>0.632151899006121</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>19.36557216431215</v>
+        <v>18.28970704407258</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08502405878119651</v>
+        <v>0.08493229507290075</v>
       </c>
       <c r="C20">
-        <v>8548.504947380716</v>
+        <v>8459.627443976593</v>
       </c>
       <c r="D20">
-        <v>9435.236947380714</v>
+        <v>9441.383443976592</v>
       </c>
       <c r="E20">
-        <v>-5961.168000000001</v>
+        <v>-5866.144</v>
       </c>
       <c r="F20">
-        <v>1710.432</v>
+        <v>1805.456</v>
       </c>
       <c r="G20">
         <v>823.7</v>
@@ -2927,28 +2927,28 @@
         <v>1573.55</v>
       </c>
       <c r="M20">
-        <v>86.03472959999999</v>
+        <v>90.8144368</v>
       </c>
       <c r="N20">
-        <v>1487.5152704</v>
+        <v>1482.7355632</v>
       </c>
       <c r="O20">
-        <v>223.12729056</v>
+        <v>222.41033448</v>
       </c>
       <c r="P20">
-        <v>1264.38797984</v>
+        <v>1260.32522872</v>
       </c>
       <c r="Q20">
-        <v>2809.58797984</v>
+        <v>2805.52522872</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09430263265999575</v>
+        <v>0.09482573465790214</v>
       </c>
       <c r="T20">
-        <v>0.632151899006121</v>
+        <v>0.6389696716344336</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.28970704407259</v>
+        <v>17.32709088385824</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08493229507290075</v>
+        <v>0.08484053136460495</v>
       </c>
       <c r="C21">
-        <v>8459.627443976593</v>
+        <v>8370.757953947807</v>
       </c>
       <c r="D21">
-        <v>9441.383443976592</v>
+        <v>9447.537953947805</v>
       </c>
       <c r="E21">
-        <v>-5866.144</v>
+        <v>-5771.120000000001</v>
       </c>
       <c r="F21">
-        <v>1805.456</v>
+        <v>1900.48</v>
       </c>
       <c r="G21">
         <v>823.7</v>
@@ -3009,28 +3009,28 @@
         <v>1573.55</v>
       </c>
       <c r="M21">
-        <v>90.8144368</v>
+        <v>95.594144</v>
       </c>
       <c r="N21">
-        <v>1482.7355632</v>
+        <v>1477.955856</v>
       </c>
       <c r="O21">
-        <v>222.41033448</v>
+        <v>221.6933784</v>
       </c>
       <c r="P21">
-        <v>1260.32522872</v>
+        <v>1256.2624776</v>
       </c>
       <c r="Q21">
-        <v>2805.52522872</v>
+        <v>2801.4624776</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09482573465790214</v>
+        <v>0.09536191420575618</v>
       </c>
       <c r="T21">
-        <v>0.6389696716344336</v>
+        <v>0.645957888578454</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.32709088385824</v>
+        <v>16.46073633966532</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08484053136460495</v>
+        <v>0.08474876765630918</v>
       </c>
       <c r="C22">
-        <v>8370.757953947807</v>
+        <v>8281.896492975489</v>
       </c>
       <c r="D22">
-        <v>9447.537953947805</v>
+        <v>9453.700492975489</v>
       </c>
       <c r="E22">
-        <v>-5771.120000000001</v>
+        <v>-5676.096</v>
       </c>
       <c r="F22">
-        <v>1900.48</v>
+        <v>1995.504</v>
       </c>
       <c r="G22">
         <v>823.7</v>
@@ -3091,28 +3091,28 @@
         <v>1573.55</v>
       </c>
       <c r="M22">
-        <v>95.594144</v>
+        <v>100.3738512</v>
       </c>
       <c r="N22">
-        <v>1477.955856</v>
+        <v>1473.1761488</v>
       </c>
       <c r="O22">
-        <v>221.6933784</v>
+        <v>220.97642232</v>
       </c>
       <c r="P22">
-        <v>1256.2624776</v>
+        <v>1252.19972648</v>
       </c>
       <c r="Q22">
-        <v>2801.4624776</v>
+        <v>2797.39972648</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09536191420575618</v>
+        <v>0.09591166791937869</v>
       </c>
       <c r="T22">
-        <v>0.645957888578454</v>
+        <v>0.6531230224071333</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.46073633966532</v>
+        <v>15.67689175206221</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08474876765630918</v>
+        <v>0.0846570039480134</v>
       </c>
       <c r="C23">
-        <v>8281.896492975491</v>
+        <v>8193.043076781738</v>
       </c>
       <c r="D23">
-        <v>9453.700492975489</v>
+        <v>9459.871076781737</v>
       </c>
       <c r="E23">
-        <v>-5676.096</v>
+        <v>-5581.072</v>
       </c>
       <c r="F23">
-        <v>1995.504</v>
+        <v>2090.528</v>
       </c>
       <c r="G23">
         <v>823.7</v>
@@ -3173,28 +3173,28 @@
         <v>1573.55</v>
       </c>
       <c r="M23">
-        <v>100.3738512</v>
+        <v>105.1535584</v>
       </c>
       <c r="N23">
-        <v>1473.1761488</v>
+        <v>1468.3964416</v>
       </c>
       <c r="O23">
-        <v>220.97642232</v>
+        <v>220.25946624</v>
       </c>
       <c r="P23">
-        <v>1252.19972648</v>
+        <v>1248.13697536</v>
       </c>
       <c r="Q23">
-        <v>2797.39972648</v>
+        <v>2793.33697536</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09591166791937869</v>
+        <v>0.09647551788206846</v>
       </c>
       <c r="T23">
-        <v>0.6531230224071332</v>
+        <v>0.660471877616035</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.67689175206221</v>
+        <v>14.96430576333212</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0846570039480134</v>
+        <v>0.08456524023971761</v>
       </c>
       <c r="C24">
-        <v>8193.043076781738</v>
+        <v>8104.197721129711</v>
       </c>
       <c r="D24">
-        <v>9459.871076781737</v>
+        <v>9466.04972112971</v>
       </c>
       <c r="E24">
-        <v>-5581.072</v>
+        <v>-5486.048000000001</v>
       </c>
       <c r="F24">
-        <v>2090.528</v>
+        <v>2185.552</v>
       </c>
       <c r="G24">
         <v>823.7</v>
@@ -3255,28 +3255,28 @@
         <v>1573.55</v>
       </c>
       <c r="M24">
-        <v>105.1535584</v>
+        <v>109.9332656</v>
       </c>
       <c r="N24">
-        <v>1468.3964416</v>
+        <v>1463.6167344</v>
       </c>
       <c r="O24">
-        <v>220.25946624</v>
+        <v>219.54251016</v>
       </c>
       <c r="P24">
-        <v>1248.13697536</v>
+        <v>1244.07422424</v>
       </c>
       <c r="Q24">
-        <v>2793.33697536</v>
+        <v>2789.27422424</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09647551788206846</v>
+        <v>0.09705401329833455</v>
       </c>
       <c r="T24">
-        <v>0.660471877616035</v>
+        <v>0.668011612181012</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.96430576333212</v>
+        <v>14.31368377362202</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08456524023971761</v>
+        <v>0.08447347653142184</v>
       </c>
       <c r="C25">
-        <v>8104.197721129711</v>
+        <v>8015.360441823776</v>
       </c>
       <c r="D25">
-        <v>9466.04972112971</v>
+        <v>9472.236441823776</v>
       </c>
       <c r="E25">
-        <v>-5486.048000000001</v>
+        <v>-5391.024</v>
       </c>
       <c r="F25">
-        <v>2185.552</v>
+        <v>2280.576</v>
       </c>
       <c r="G25">
         <v>823.7</v>
@@ -3337,28 +3337,28 @@
         <v>1573.55</v>
       </c>
       <c r="M25">
-        <v>109.9332656</v>
+        <v>114.7129728</v>
       </c>
       <c r="N25">
-        <v>1463.6167344</v>
+        <v>1458.8370272</v>
       </c>
       <c r="O25">
-        <v>219.54251016</v>
+        <v>218.82555408</v>
       </c>
       <c r="P25">
-        <v>1244.07422424</v>
+        <v>1240.01147312</v>
       </c>
       <c r="Q25">
-        <v>2789.27422424</v>
+        <v>2785.21147312</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09705401329833455</v>
+        <v>0.09764773227818663</v>
       </c>
       <c r="T25">
-        <v>0.668011612181012</v>
+        <v>0.6757497608134886</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.31368377362202</v>
+        <v>13.71728028305444</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08447347653142184</v>
+        <v>0.08438171282312604</v>
       </c>
       <c r="C26">
-        <v>8015.360441823776</v>
+        <v>7926.531254709655</v>
       </c>
       <c r="D26">
-        <v>9472.236441823776</v>
+        <v>9478.431254709654</v>
       </c>
       <c r="E26">
-        <v>-5391.024</v>
+        <v>-5296</v>
       </c>
       <c r="F26">
-        <v>2280.576</v>
+        <v>2375.6</v>
       </c>
       <c r="G26">
         <v>823.7</v>
@@ -3419,28 +3419,28 @@
         <v>1573.55</v>
       </c>
       <c r="M26">
-        <v>114.7129728</v>
+        <v>119.49268</v>
       </c>
       <c r="N26">
-        <v>1458.8370272</v>
+        <v>1454.05732</v>
       </c>
       <c r="O26">
-        <v>218.82555408</v>
+        <v>218.108598</v>
       </c>
       <c r="P26">
-        <v>1240.01147312</v>
+        <v>1235.948722</v>
       </c>
       <c r="Q26">
-        <v>2785.21147312</v>
+        <v>2781.148722</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09764773227818663</v>
+        <v>0.09825728376416806</v>
       </c>
       <c r="T26">
-        <v>0.6757497608134886</v>
+        <v>0.6836942600761644</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>13.71728028305444</v>
+        <v>13.16858907173226</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08438171282312604</v>
+        <v>0.08462144911483027</v>
       </c>
       <c r="C27">
-        <v>7926.531254709655</v>
+        <v>7815.340101425911</v>
       </c>
       <c r="D27">
-        <v>9478.431254709654</v>
+        <v>9462.26410142591</v>
       </c>
       <c r="E27">
-        <v>-5296</v>
+        <v>-5200.976000000001</v>
       </c>
       <c r="F27">
-        <v>2375.6</v>
+        <v>2470.624</v>
       </c>
       <c r="G27">
         <v>823.7</v>
@@ -3501,45 +3501,45 @@
         <v>1573.55</v>
       </c>
       <c r="M27">
-        <v>119.49268</v>
+        <v>127.9783232</v>
       </c>
       <c r="N27">
-        <v>1454.05732</v>
+        <v>1445.5716768</v>
       </c>
       <c r="O27">
-        <v>218.108598</v>
+        <v>216.83575152</v>
       </c>
       <c r="P27">
-        <v>1235.948722</v>
+        <v>1228.73592528</v>
       </c>
       <c r="Q27">
-        <v>2781.148722</v>
+        <v>2773.93592528</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09825728376416806</v>
+        <v>0.0988833096146355</v>
       </c>
       <c r="T27">
-        <v>0.6836942600761644</v>
+        <v>0.6918534755351289</v>
       </c>
       <c r="U27">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.15</v>
       </c>
       <c r="W27">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>13.16858907173226</v>
+        <v>12.29544160803632</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08462144911483027</v>
+        <v>0.08454243540653449</v>
       </c>
       <c r="C28">
-        <v>7815.340101425911</v>
+        <v>7725.638471066924</v>
       </c>
       <c r="D28">
-        <v>9462.26410142591</v>
+        <v>9467.586471066923</v>
       </c>
       <c r="E28">
-        <v>-5200.976000000001</v>
+        <v>-5105.952</v>
       </c>
       <c r="F28">
-        <v>2470.624</v>
+        <v>2565.648</v>
       </c>
       <c r="G28">
         <v>823.7</v>
@@ -3583,28 +3583,28 @@
         <v>1573.55</v>
       </c>
       <c r="M28">
-        <v>127.9783232</v>
+        <v>132.9005664</v>
       </c>
       <c r="N28">
-        <v>1445.5716768</v>
+        <v>1440.6494336</v>
       </c>
       <c r="O28">
-        <v>216.83575152</v>
+        <v>216.09741504</v>
       </c>
       <c r="P28">
-        <v>1228.73592528</v>
+        <v>1224.55201856</v>
       </c>
       <c r="Q28">
-        <v>2773.93592528</v>
+        <v>2769.75201856</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0988833096146355</v>
+        <v>0.09952648685826643</v>
       </c>
       <c r="T28">
-        <v>0.6918534755351289</v>
+        <v>0.700236231143654</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>12.29544160803632</v>
+        <v>11.84005488181275</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08454243540653449</v>
+        <v>0.08446342169823871</v>
       </c>
       <c r="C29">
-        <v>7725.638471066924</v>
+        <v>7635.942831570394</v>
       </c>
       <c r="D29">
-        <v>9467.586471066923</v>
+        <v>9472.914831570393</v>
       </c>
       <c r="E29">
-        <v>-5105.952</v>
+        <v>-5010.928</v>
       </c>
       <c r="F29">
-        <v>2565.648</v>
+        <v>2660.672</v>
       </c>
       <c r="G29">
         <v>823.7</v>
@@ -3665,28 +3665,28 @@
         <v>1573.55</v>
       </c>
       <c r="M29">
-        <v>132.9005664</v>
+        <v>137.8228096</v>
       </c>
       <c r="N29">
-        <v>1440.6494336</v>
+        <v>1435.7271904</v>
       </c>
       <c r="O29">
-        <v>216.09741504</v>
+        <v>215.35907856</v>
       </c>
       <c r="P29">
-        <v>1224.55201856</v>
+        <v>1220.36811184</v>
       </c>
       <c r="Q29">
-        <v>2769.75201856</v>
+        <v>2765.56811184</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09952648685826643</v>
+        <v>0.1001875301364427</v>
       </c>
       <c r="T29">
-        <v>0.700236231143654</v>
+        <v>0.7088518410746382</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.84005488181275</v>
+        <v>11.41719577889087</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08446342169823871</v>
+        <v>0.08438440798994293</v>
       </c>
       <c r="C30">
-        <v>7635.942831570394</v>
+        <v>7546.253193056995</v>
       </c>
       <c r="D30">
-        <v>9472.914831570393</v>
+        <v>9478.249193056994</v>
       </c>
       <c r="E30">
-        <v>-5010.928</v>
+        <v>-4915.904</v>
       </c>
       <c r="F30">
-        <v>2660.672</v>
+        <v>2755.696</v>
       </c>
       <c r="G30">
         <v>823.7</v>
@@ -3747,28 +3747,28 @@
         <v>1573.55</v>
       </c>
       <c r="M30">
-        <v>137.8228096</v>
+        <v>142.7450528</v>
       </c>
       <c r="N30">
-        <v>1435.7271904</v>
+        <v>1430.8049472</v>
       </c>
       <c r="O30">
-        <v>215.35907856</v>
+        <v>214.62074208</v>
       </c>
       <c r="P30">
-        <v>1220.36811184</v>
+        <v>1216.18420512</v>
       </c>
       <c r="Q30">
-        <v>2765.56811184</v>
+        <v>2761.38420512</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1001875301364427</v>
+        <v>0.1008671943520323</v>
       </c>
       <c r="T30">
-        <v>0.7088518410746382</v>
+        <v>0.7177101442431147</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.41719577889087</v>
+        <v>11.02349937272222</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08438440798994293</v>
+        <v>0.08430539428164714</v>
       </c>
       <c r="C31">
-        <v>7546.253193056995</v>
+        <v>7456.569565670214</v>
       </c>
       <c r="D31">
-        <v>9478.249193056994</v>
+        <v>9483.589565670212</v>
       </c>
       <c r="E31">
-        <v>-4915.904</v>
+        <v>-4820.880000000001</v>
       </c>
       <c r="F31">
-        <v>2755.696</v>
+        <v>2850.72</v>
       </c>
       <c r="G31">
         <v>823.7</v>
@@ -3829,28 +3829,28 @@
         <v>1573.55</v>
       </c>
       <c r="M31">
-        <v>142.7450528</v>
+        <v>147.667296</v>
       </c>
       <c r="N31">
-        <v>1430.8049472</v>
+        <v>1425.882704</v>
       </c>
       <c r="O31">
-        <v>214.62074208</v>
+        <v>213.8824056</v>
       </c>
       <c r="P31">
-        <v>1216.18420512</v>
+        <v>1212.0002984</v>
       </c>
       <c r="Q31">
-        <v>2761.38420512</v>
+        <v>2757.2002984</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1008671943520323</v>
+        <v>0.1015662775452102</v>
       </c>
       <c r="T31">
-        <v>0.7177101442431147</v>
+        <v>0.7268215417878334</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.02349937272222</v>
+        <v>10.65604939363148</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08430539428164714</v>
+        <v>0.08422638057335137</v>
       </c>
       <c r="C32">
-        <v>7456.569565670214</v>
+        <v>7366.891959576399</v>
       </c>
       <c r="D32">
-        <v>9483.589565670212</v>
+        <v>9488.935959576398</v>
       </c>
       <c r="E32">
-        <v>-4820.880000000001</v>
+        <v>-4725.856000000001</v>
       </c>
       <c r="F32">
-        <v>2850.72</v>
+        <v>2945.744</v>
       </c>
       <c r="G32">
         <v>823.7</v>
@@ -3911,28 +3911,28 @@
         <v>1573.55</v>
       </c>
       <c r="M32">
-        <v>147.667296</v>
+        <v>152.5895392</v>
       </c>
       <c r="N32">
-        <v>1425.882704</v>
+        <v>1420.9604608</v>
       </c>
       <c r="O32">
-        <v>213.8824056</v>
+        <v>213.14406912</v>
       </c>
       <c r="P32">
-        <v>1212.0002984</v>
+        <v>1207.81639168</v>
       </c>
       <c r="Q32">
-        <v>2757.2002984</v>
+        <v>2753.01639168</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1015662775452102</v>
+        <v>0.1022856240193498</v>
       </c>
       <c r="T32">
-        <v>0.7268215417878334</v>
+        <v>0.7361970378121093</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.65604939363148</v>
+        <v>10.31230586480466</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08422638057335137</v>
+        <v>0.08414736686505558</v>
       </c>
       <c r="C33">
-        <v>7366.891959576399</v>
+        <v>7277.220384964854</v>
       </c>
       <c r="D33">
-        <v>9488.935959576398</v>
+        <v>9494.288384964853</v>
       </c>
       <c r="E33">
-        <v>-4725.856000000001</v>
+        <v>-4630.832</v>
       </c>
       <c r="F33">
-        <v>2945.744</v>
+        <v>3040.768</v>
       </c>
       <c r="G33">
         <v>823.7</v>
@@ -3993,28 +3993,28 @@
         <v>1573.55</v>
       </c>
       <c r="M33">
-        <v>152.5895392</v>
+        <v>157.5117824</v>
       </c>
       <c r="N33">
-        <v>1420.9604608</v>
+        <v>1416.0382176</v>
       </c>
       <c r="O33">
-        <v>213.14406912</v>
+        <v>212.40573264</v>
       </c>
       <c r="P33">
-        <v>1207.81639168</v>
+        <v>1203.63248496</v>
       </c>
       <c r="Q33">
-        <v>2753.01639168</v>
+        <v>2748.83248496</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1022856240193498</v>
+        <v>0.1030261277427288</v>
       </c>
       <c r="T33">
-        <v>0.7361970378121093</v>
+        <v>0.7458482837194521</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.31230586480466</v>
+        <v>9.990046306529512</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08414736686505558</v>
+        <v>0.0845452031567598</v>
       </c>
       <c r="C34">
-        <v>7277.220384964854</v>
+        <v>7155.307934001021</v>
       </c>
       <c r="D34">
-        <v>9494.288384964853</v>
+        <v>9467.39993400102</v>
       </c>
       <c r="E34">
-        <v>-4630.832</v>
+        <v>-4535.808000000001</v>
       </c>
       <c r="F34">
-        <v>3040.768</v>
+        <v>3135.792</v>
       </c>
       <c r="G34">
         <v>823.7</v>
@@ -4075,45 +4075,45 @@
         <v>1573.55</v>
       </c>
       <c r="M34">
-        <v>157.5117824</v>
+        <v>167.764872</v>
       </c>
       <c r="N34">
-        <v>1416.0382176</v>
+        <v>1405.785128</v>
       </c>
       <c r="O34">
-        <v>212.40573264</v>
+        <v>210.8677692</v>
       </c>
       <c r="P34">
-        <v>1203.63248496</v>
+        <v>1194.9173588</v>
       </c>
       <c r="Q34">
-        <v>2748.83248496</v>
+        <v>2740.1173588</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1030261277427288</v>
+        <v>0.1037887360548654</v>
       </c>
       <c r="T34">
-        <v>0.7458482837194521</v>
+        <v>0.7557876265195514</v>
       </c>
       <c r="U34">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V34">
         <v>0.15</v>
       </c>
       <c r="W34">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>9.990046306529512</v>
+        <v>9.37949632268667</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0845452031567598</v>
+        <v>0.08448063944846403</v>
       </c>
       <c r="C35">
-        <v>7155.307934001021</v>
+        <v>7064.63722608774</v>
       </c>
       <c r="D35">
-        <v>9467.39993400102</v>
+        <v>9471.75322608774</v>
       </c>
       <c r="E35">
-        <v>-4535.808000000001</v>
+        <v>-4440.784</v>
       </c>
       <c r="F35">
-        <v>3135.792</v>
+        <v>3230.816</v>
       </c>
       <c r="G35">
         <v>823.7</v>
@@ -4157,28 +4157,28 @@
         <v>1573.55</v>
       </c>
       <c r="M35">
-        <v>167.764872</v>
+        <v>172.848656</v>
       </c>
       <c r="N35">
-        <v>1405.785128</v>
+        <v>1400.701344</v>
       </c>
       <c r="O35">
-        <v>210.8677692</v>
+        <v>210.1052016</v>
       </c>
       <c r="P35">
-        <v>1194.9173588</v>
+        <v>1190.5961424</v>
       </c>
       <c r="Q35">
-        <v>2740.1173588</v>
+        <v>2735.7961424</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1037887360548654</v>
+        <v>0.104574453709794</v>
       </c>
       <c r="T35">
-        <v>0.7557876265195514</v>
+        <v>0.7660281615257144</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.37949632268667</v>
+        <v>9.103628783784121</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08448063944846403</v>
+        <v>0.08441607574016824</v>
       </c>
       <c r="C36">
-        <v>7064.63722608774</v>
+        <v>6973.97052347058</v>
       </c>
       <c r="D36">
-        <v>9471.75322608774</v>
+        <v>9476.110523470579</v>
       </c>
       <c r="E36">
-        <v>-4440.784</v>
+        <v>-4345.76</v>
       </c>
       <c r="F36">
-        <v>3230.816</v>
+        <v>3325.84</v>
       </c>
       <c r="G36">
         <v>823.7</v>
@@ -4239,28 +4239,28 @@
         <v>1573.55</v>
       </c>
       <c r="M36">
-        <v>172.848656</v>
+        <v>177.93244</v>
       </c>
       <c r="N36">
-        <v>1400.701344</v>
+        <v>1395.61756</v>
       </c>
       <c r="O36">
-        <v>210.1052016</v>
+        <v>209.342634</v>
       </c>
       <c r="P36">
-        <v>1190.5961424</v>
+        <v>1186.274926</v>
       </c>
       <c r="Q36">
-        <v>2735.7961424</v>
+        <v>2731.474926</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.104574453709794</v>
+        <v>0.1053843472925665</v>
       </c>
       <c r="T36">
-        <v>0.7660281615257144</v>
+        <v>0.7765837899166824</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.103628783784121</v>
+        <v>8.843525104247432</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08441607574016824</v>
+        <v>0.08435151203187244</v>
       </c>
       <c r="C37">
-        <v>6973.97052347058</v>
+        <v>6883.307831679759</v>
       </c>
       <c r="D37">
-        <v>9476.110523470579</v>
+        <v>9480.471831679759</v>
       </c>
       <c r="E37">
-        <v>-4345.76</v>
+        <v>-4250.736</v>
       </c>
       <c r="F37">
-        <v>3325.84</v>
+        <v>3420.864</v>
       </c>
       <c r="G37">
         <v>823.7</v>
@@ -4321,28 +4321,28 @@
         <v>1573.55</v>
       </c>
       <c r="M37">
-        <v>177.93244</v>
+        <v>183.016224</v>
       </c>
       <c r="N37">
-        <v>1395.61756</v>
+        <v>1390.533776</v>
       </c>
       <c r="O37">
-        <v>209.342634</v>
+        <v>208.5800664</v>
       </c>
       <c r="P37">
-        <v>1186.274926</v>
+        <v>1181.9537096</v>
       </c>
       <c r="Q37">
-        <v>2731.474926</v>
+        <v>2727.1537096</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1053843472925665</v>
+        <v>0.1062195500498007</v>
       </c>
       <c r="T37">
-        <v>0.7765837899166824</v>
+        <v>0.7874692816948681</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.843525104247432</v>
+        <v>8.597871629129447</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08435151203187245</v>
+        <v>0.08428694832357668</v>
       </c>
       <c r="C38">
-        <v>6883.30783167976</v>
+        <v>6792.649156255688</v>
       </c>
       <c r="D38">
-        <v>9480.471831679759</v>
+        <v>9484.837156255688</v>
       </c>
       <c r="E38">
-        <v>-4250.736000000001</v>
+        <v>-4155.712</v>
       </c>
       <c r="F38">
-        <v>3420.864</v>
+        <v>3515.888</v>
       </c>
       <c r="G38">
         <v>823.7</v>
@@ -4403,28 +4403,28 @@
         <v>1573.55</v>
       </c>
       <c r="M38">
-        <v>183.016224</v>
+        <v>188.100008</v>
       </c>
       <c r="N38">
-        <v>1390.533776</v>
+        <v>1385.449992</v>
       </c>
       <c r="O38">
-        <v>208.5800664</v>
+        <v>207.8174988</v>
       </c>
       <c r="P38">
-        <v>1181.9537096</v>
+        <v>1177.6324932</v>
       </c>
       <c r="Q38">
-        <v>2727.1537096</v>
+        <v>2722.8324932</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1062195500498007</v>
+        <v>0.1070812671802804</v>
       </c>
       <c r="T38">
-        <v>0.787469281694868</v>
+        <v>0.7987003446406151</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.59787162912945</v>
+        <v>8.365496720234056</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08428694832357668</v>
+        <v>0.08422238461528089</v>
       </c>
       <c r="C39">
-        <v>6792.649156255688</v>
+        <v>6701.994502748979</v>
       </c>
       <c r="D39">
-        <v>9484.837156255688</v>
+        <v>9489.206502748979</v>
       </c>
       <c r="E39">
-        <v>-4155.712</v>
+        <v>-4060.688000000001</v>
       </c>
       <c r="F39">
-        <v>3515.888</v>
+        <v>3610.912</v>
       </c>
       <c r="G39">
         <v>823.7</v>
@@ -4485,28 +4485,28 @@
         <v>1573.55</v>
       </c>
       <c r="M39">
-        <v>188.100008</v>
+        <v>193.183792</v>
       </c>
       <c r="N39">
-        <v>1385.449992</v>
+        <v>1380.366208</v>
       </c>
       <c r="O39">
-        <v>207.8174988</v>
+        <v>207.0549312</v>
       </c>
       <c r="P39">
-        <v>1177.6324932</v>
+        <v>1173.3112768</v>
       </c>
       <c r="Q39">
-        <v>2722.8324932</v>
+        <v>2718.5112768</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1070812671802804</v>
+        <v>0.1079707816375498</v>
       </c>
       <c r="T39">
-        <v>0.7987003446406151</v>
+        <v>0.8102936999394509</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.365496720234056</v>
+        <v>8.145352069701582</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08422238461528089</v>
+        <v>0.08415782090698511</v>
       </c>
       <c r="C40">
-        <v>6701.994502748979</v>
+        <v>6611.343876720484</v>
       </c>
       <c r="D40">
-        <v>9489.206502748979</v>
+        <v>9493.579876720483</v>
       </c>
       <c r="E40">
-        <v>-4060.688000000001</v>
+        <v>-3965.664</v>
       </c>
       <c r="F40">
-        <v>3610.912</v>
+        <v>3705.936</v>
       </c>
       <c r="G40">
         <v>823.7</v>
@@ -4567,28 +4567,28 @@
         <v>1573.55</v>
       </c>
       <c r="M40">
-        <v>193.183792</v>
+        <v>198.267576</v>
       </c>
       <c r="N40">
-        <v>1380.366208</v>
+        <v>1375.282424</v>
       </c>
       <c r="O40">
-        <v>207.0549312</v>
+        <v>206.2923636</v>
       </c>
       <c r="P40">
-        <v>1173.3112768</v>
+        <v>1168.9900604</v>
       </c>
       <c r="Q40">
-        <v>2718.5112768</v>
+        <v>2714.1900604</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1079707816375498</v>
+        <v>0.1088894605032543</v>
       </c>
       <c r="T40">
-        <v>0.8102936999394509</v>
+        <v>0.8222671652480845</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.145352069701582</v>
+        <v>7.936496888427183</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08415782090698511</v>
+        <v>0.08409325719868933</v>
       </c>
       <c r="C41">
-        <v>6611.343876720484</v>
+        <v>6520.697283741308</v>
       </c>
       <c r="D41">
-        <v>9493.579876720483</v>
+        <v>9497.957283741307</v>
       </c>
       <c r="E41">
-        <v>-3965.664</v>
+        <v>-3870.64</v>
       </c>
       <c r="F41">
-        <v>3705.936</v>
+        <v>3800.96</v>
       </c>
       <c r="G41">
         <v>823.7</v>
@@ -4649,28 +4649,28 @@
         <v>1573.55</v>
       </c>
       <c r="M41">
-        <v>198.267576</v>
+        <v>203.35136</v>
       </c>
       <c r="N41">
-        <v>1375.282424</v>
+        <v>1370.19864</v>
       </c>
       <c r="O41">
-        <v>206.2923636</v>
+        <v>205.529796</v>
       </c>
       <c r="P41">
-        <v>1168.9900604</v>
+        <v>1164.668844</v>
       </c>
       <c r="Q41">
-        <v>2714.1900604</v>
+        <v>2709.868844</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1088894605032543</v>
+        <v>0.1098387619978156</v>
       </c>
       <c r="T41">
-        <v>0.8222671652480845</v>
+        <v>0.8346397460670061</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.936496888427183</v>
+        <v>7.738084466216503</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08409325719868933</v>
+        <v>0.08430749349039354</v>
       </c>
       <c r="C42">
-        <v>6520.697283741308</v>
+        <v>6411.163606690552</v>
       </c>
       <c r="D42">
-        <v>9497.957283741307</v>
+        <v>9483.447606690552</v>
       </c>
       <c r="E42">
-        <v>-3870.64</v>
+        <v>-3775.616</v>
       </c>
       <c r="F42">
-        <v>3800.96</v>
+        <v>3895.984</v>
       </c>
       <c r="G42">
         <v>823.7</v>
@@ -4731,45 +4731,45 @@
         <v>1573.55</v>
       </c>
       <c r="M42">
-        <v>203.35136</v>
+        <v>211.5519312</v>
       </c>
       <c r="N42">
-        <v>1370.19864</v>
+        <v>1361.9980688</v>
       </c>
       <c r="O42">
-        <v>205.529796</v>
+        <v>204.29971032</v>
       </c>
       <c r="P42">
-        <v>1164.668844</v>
+        <v>1157.69835848</v>
       </c>
       <c r="Q42">
-        <v>2709.868844</v>
+        <v>2702.89835848</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1098387619978156</v>
+        <v>0.1108202432040569</v>
       </c>
       <c r="T42">
-        <v>0.8346397460670061</v>
+        <v>0.8474317364052129</v>
       </c>
       <c r="U42">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V42">
         <v>0.15</v>
       </c>
       <c r="W42">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y42">
-        <v>7.738084466216503</v>
+        <v>7.438126379060916</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08430749349039354</v>
+        <v>0.08424972978209778</v>
       </c>
       <c r="C43">
-        <v>6411.163606690552</v>
+        <v>6320.047428289792</v>
       </c>
       <c r="D43">
-        <v>9483.447606690552</v>
+        <v>9487.355428289791</v>
       </c>
       <c r="E43">
-        <v>-3775.616</v>
+        <v>-3680.592</v>
       </c>
       <c r="F43">
-        <v>3895.984</v>
+        <v>3991.008</v>
       </c>
       <c r="G43">
         <v>823.7</v>
@@ -4813,28 +4813,28 @@
         <v>1573.55</v>
       </c>
       <c r="M43">
-        <v>211.5519312</v>
+        <v>216.7117344</v>
       </c>
       <c r="N43">
-        <v>1361.9980688</v>
+        <v>1356.8382656</v>
       </c>
       <c r="O43">
-        <v>204.29971032</v>
+        <v>203.52573984</v>
       </c>
       <c r="P43">
-        <v>1157.69835848</v>
+        <v>1153.31252576</v>
       </c>
       <c r="Q43">
-        <v>2702.89835848</v>
+        <v>2698.51252576</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1108202432040569</v>
+        <v>0.1118355685898238</v>
       </c>
       <c r="T43">
-        <v>0.8474317364052129</v>
+        <v>0.8606648298585304</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.438126379060916</v>
+        <v>7.261028131940417</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08424972978209778</v>
+        <v>0.084191966073802</v>
       </c>
       <c r="C44">
-        <v>6320.047428289792</v>
+        <v>6228.934471790099</v>
       </c>
       <c r="D44">
-        <v>9487.355428289791</v>
+        <v>9491.266471790097</v>
       </c>
       <c r="E44">
-        <v>-3680.592000000001</v>
+        <v>-3585.568000000001</v>
       </c>
       <c r="F44">
-        <v>3991.008</v>
+        <v>4086.032</v>
       </c>
       <c r="G44">
         <v>823.7</v>
@@ -4895,28 +4895,28 @@
         <v>1573.55</v>
       </c>
       <c r="M44">
-        <v>216.7117344</v>
+        <v>221.8715376</v>
       </c>
       <c r="N44">
-        <v>1356.8382656</v>
+        <v>1351.6784624</v>
       </c>
       <c r="O44">
-        <v>203.52573984</v>
+        <v>202.75176936</v>
       </c>
       <c r="P44">
-        <v>1153.31252576</v>
+        <v>1148.92669304</v>
       </c>
       <c r="Q44">
-        <v>2698.51252576</v>
+        <v>2694.12669304</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1118355685898237</v>
+        <v>0.1128865194277228</v>
       </c>
       <c r="T44">
-        <v>0.8606648298585303</v>
+        <v>0.8743622423803853</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.261028131940418</v>
+        <v>7.092167012592967</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.084191966073802</v>
+        <v>0.0841342023655062</v>
       </c>
       <c r="C45">
-        <v>6228.934471790099</v>
+        <v>6137.824741177673</v>
       </c>
       <c r="D45">
-        <v>9491.266471790097</v>
+        <v>9495.180741177672</v>
       </c>
       <c r="E45">
-        <v>-3585.568000000001</v>
+        <v>-3490.544000000001</v>
       </c>
       <c r="F45">
-        <v>4086.032</v>
+        <v>4181.056</v>
       </c>
       <c r="G45">
         <v>823.7</v>
@@ -4977,28 +4977,28 @@
         <v>1573.55</v>
       </c>
       <c r="M45">
-        <v>221.8715376</v>
+        <v>227.0313408</v>
       </c>
       <c r="N45">
-        <v>1351.6784624</v>
+        <v>1346.5186592</v>
       </c>
       <c r="O45">
-        <v>202.75176936</v>
+        <v>201.97779888</v>
       </c>
       <c r="P45">
-        <v>1148.92669304</v>
+        <v>1144.54086032</v>
       </c>
       <c r="Q45">
-        <v>2694.12669304</v>
+        <v>2689.74086032</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1128865194277228</v>
+        <v>0.1139750042241182</v>
       </c>
       <c r="T45">
-        <v>0.8743622423803853</v>
+        <v>0.8885488482065921</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.092167012592967</v>
+        <v>6.930981398670399</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0841342023655062</v>
+        <v>0.08407643865721043</v>
       </c>
       <c r="C46">
-        <v>6137.824741177673</v>
+        <v>6046.718240445305</v>
       </c>
       <c r="D46">
-        <v>9495.180741177672</v>
+        <v>9499.098240445304</v>
       </c>
       <c r="E46">
-        <v>-3490.544000000001</v>
+        <v>-3395.52</v>
       </c>
       <c r="F46">
-        <v>4181.056</v>
+        <v>4276.08</v>
       </c>
       <c r="G46">
         <v>823.7</v>
@@ -5059,28 +5059,28 @@
         <v>1573.55</v>
       </c>
       <c r="M46">
-        <v>227.0313408</v>
+        <v>232.191144</v>
       </c>
       <c r="N46">
-        <v>1346.5186592</v>
+        <v>1341.358856</v>
       </c>
       <c r="O46">
-        <v>201.97779888</v>
+        <v>201.2038284</v>
       </c>
       <c r="P46">
-        <v>1144.54086032</v>
+        <v>1140.1550276</v>
       </c>
       <c r="Q46">
-        <v>2689.74086032</v>
+        <v>2685.3550276</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1139750042241182</v>
+        <v>0.1151030702858371</v>
       </c>
       <c r="T46">
-        <v>0.8885488482065921</v>
+        <v>0.9032513306082974</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.930981398670399</v>
+        <v>6.776959589811056</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08407643865721043</v>
+        <v>0.08401867494891466</v>
       </c>
       <c r="C47">
-        <v>6046.718240445305</v>
+        <v>5955.614973592373</v>
       </c>
       <c r="D47">
-        <v>9499.098240445304</v>
+        <v>9503.018973592372</v>
       </c>
       <c r="E47">
-        <v>-3395.52</v>
+        <v>-3300.496</v>
       </c>
       <c r="F47">
-        <v>4276.08</v>
+        <v>4371.104</v>
       </c>
       <c r="G47">
         <v>823.7</v>
@@ -5141,28 +5141,28 @@
         <v>1573.55</v>
       </c>
       <c r="M47">
-        <v>232.191144</v>
+        <v>237.3509472</v>
       </c>
       <c r="N47">
-        <v>1341.358856</v>
+        <v>1336.1990528</v>
       </c>
       <c r="O47">
-        <v>201.2038284</v>
+        <v>200.42985792</v>
       </c>
       <c r="P47">
-        <v>1140.1550276</v>
+        <v>1135.76919488</v>
       </c>
       <c r="Q47">
-        <v>2685.3550276</v>
+        <v>2680.96919488</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1151030702858371</v>
+        <v>0.1162729165720642</v>
       </c>
       <c r="T47">
-        <v>0.9032513306082974</v>
+        <v>0.9184983493952512</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.776959589811056</v>
+        <v>6.629634381336903</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08401867494891466</v>
+        <v>0.08396091124061887</v>
       </c>
       <c r="C48">
-        <v>5955.614973592373</v>
+        <v>5864.514944624864</v>
       </c>
       <c r="D48">
-        <v>9503.018973592372</v>
+        <v>9506.942944624863</v>
       </c>
       <c r="E48">
-        <v>-3300.496</v>
+        <v>-3205.472000000001</v>
       </c>
       <c r="F48">
-        <v>4371.104</v>
+        <v>4466.128</v>
       </c>
       <c r="G48">
         <v>823.7</v>
@@ -5223,28 +5223,28 @@
         <v>1573.55</v>
       </c>
       <c r="M48">
-        <v>237.3509472</v>
+        <v>242.5107504</v>
       </c>
       <c r="N48">
-        <v>1336.1990528</v>
+        <v>1331.0392496</v>
       </c>
       <c r="O48">
-        <v>200.42985792</v>
+        <v>199.65588744</v>
       </c>
       <c r="P48">
-        <v>1135.76919488</v>
+        <v>1131.38336216</v>
       </c>
       <c r="Q48">
-        <v>2680.96919488</v>
+        <v>2676.58336216</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1162729165720642</v>
+        <v>0.1174869080011677</v>
       </c>
       <c r="T48">
-        <v>0.9184983493952512</v>
+        <v>0.9343207273817126</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.629634381336903</v>
+        <v>6.488578330670161</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08396091124061887</v>
+        <v>0.08390314753232309</v>
       </c>
       <c r="C49">
-        <v>5864.514944624864</v>
+        <v>5773.418157555379</v>
       </c>
       <c r="D49">
-        <v>9506.942944624863</v>
+        <v>9510.870157555379</v>
       </c>
       <c r="E49">
-        <v>-3205.472000000001</v>
+        <v>-3110.448</v>
       </c>
       <c r="F49">
-        <v>4466.128</v>
+        <v>4561.152</v>
       </c>
       <c r="G49">
         <v>823.7</v>
@@ -5305,28 +5305,28 @@
         <v>1573.55</v>
       </c>
       <c r="M49">
-        <v>242.5107504</v>
+        <v>247.6705536</v>
       </c>
       <c r="N49">
-        <v>1331.0392496</v>
+        <v>1325.8794464</v>
       </c>
       <c r="O49">
-        <v>199.65588744</v>
+        <v>198.88191696</v>
       </c>
       <c r="P49">
-        <v>1131.38336216</v>
+        <v>1126.99752944</v>
       </c>
       <c r="Q49">
-        <v>2676.58336216</v>
+        <v>2672.19752944</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1174869080011677</v>
+        <v>0.1187475914083136</v>
       </c>
       <c r="T49">
-        <v>0.9343207273817126</v>
+        <v>0.9507516583676532</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.488578330670161</v>
+        <v>6.353399615447866</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08390314753232309</v>
+        <v>0.0838453838240273</v>
       </c>
       <c r="C50">
-        <v>5773.418157555379</v>
+        <v>5682.324616403157</v>
       </c>
       <c r="D50">
-        <v>9510.870157555379</v>
+        <v>9514.800616403156</v>
       </c>
       <c r="E50">
-        <v>-3110.448</v>
+        <v>-3015.424000000001</v>
       </c>
       <c r="F50">
-        <v>4561.152</v>
+        <v>4656.175999999999</v>
       </c>
       <c r="G50">
         <v>823.7</v>
@@ -5387,28 +5387,28 @@
         <v>1573.55</v>
       </c>
       <c r="M50">
-        <v>247.6705536</v>
+        <v>252.8303568</v>
       </c>
       <c r="N50">
-        <v>1325.8794464</v>
+        <v>1320.7196432</v>
       </c>
       <c r="O50">
-        <v>198.88191696</v>
+        <v>198.10794648</v>
       </c>
       <c r="P50">
-        <v>1126.99752944</v>
+        <v>1122.61169672</v>
       </c>
       <c r="Q50">
-        <v>2672.19752944</v>
+        <v>2667.81169672</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1187475914083136</v>
+        <v>0.1200577133804457</v>
       </c>
       <c r="T50">
-        <v>0.9507516583676532</v>
+        <v>0.9678269395883365</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.353399615447866</v>
+        <v>6.223738398806073</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0838453838240273</v>
+        <v>0.08421262011573152</v>
       </c>
       <c r="C51">
-        <v>5682.324616403157</v>
+        <v>5562.367665360526</v>
       </c>
       <c r="D51">
-        <v>9514.800616403156</v>
+        <v>9489.867665360525</v>
       </c>
       <c r="E51">
-        <v>-3015.424000000001</v>
+        <v>-2920.400000000001</v>
       </c>
       <c r="F51">
-        <v>4656.175999999999</v>
+        <v>4751.2</v>
       </c>
       <c r="G51">
         <v>823.7</v>
@@ -5469,45 +5469,45 @@
         <v>1573.55</v>
       </c>
       <c r="M51">
-        <v>252.8303568</v>
+        <v>262.74136</v>
       </c>
       <c r="N51">
-        <v>1320.7196432</v>
+        <v>1310.80864</v>
       </c>
       <c r="O51">
-        <v>198.10794648</v>
+        <v>196.621296</v>
       </c>
       <c r="P51">
-        <v>1122.61169672</v>
+        <v>1114.187344</v>
       </c>
       <c r="Q51">
-        <v>2667.81169672</v>
+        <v>2659.387344</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1200577133804457</v>
+        <v>0.1214202402314631</v>
       </c>
       <c r="T51">
-        <v>0.9678269395883365</v>
+        <v>0.9855852320578475</v>
       </c>
       <c r="U51">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V51">
         <v>0.15</v>
       </c>
       <c r="W51">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>6.223738398806073</v>
+        <v>5.988969532623261</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08421262011573152</v>
+        <v>0.08416335640743575</v>
       </c>
       <c r="C52">
-        <v>5562.367665360526</v>
+        <v>5470.68075864628</v>
       </c>
       <c r="D52">
-        <v>9489.867665360525</v>
+        <v>9493.20475864628</v>
       </c>
       <c r="E52">
-        <v>-2920.400000000001</v>
+        <v>-2825.376</v>
       </c>
       <c r="F52">
-        <v>4751.2</v>
+        <v>4846.224</v>
       </c>
       <c r="G52">
         <v>823.7</v>
@@ -5551,28 +5551,28 @@
         <v>1573.55</v>
       </c>
       <c r="M52">
-        <v>262.74136</v>
+        <v>267.9961872</v>
       </c>
       <c r="N52">
-        <v>1310.80864</v>
+        <v>1305.5538128</v>
       </c>
       <c r="O52">
-        <v>196.621296</v>
+        <v>195.83307192</v>
       </c>
       <c r="P52">
-        <v>1114.187344</v>
+        <v>1109.72074088</v>
       </c>
       <c r="Q52">
-        <v>2659.387344</v>
+        <v>2654.92074088</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1214202402314631</v>
+        <v>0.1228383804233383</v>
       </c>
       <c r="T52">
-        <v>0.9855852320578475</v>
+        <v>1.00406835279142</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.988969532623261</v>
+        <v>5.871538757473784</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08416335640743575</v>
+        <v>0.08411409269913997</v>
       </c>
       <c r="C53">
-        <v>5470.68075864628</v>
+        <v>5378.9961997222</v>
       </c>
       <c r="D53">
-        <v>9493.20475864628</v>
+        <v>9496.544199722199</v>
       </c>
       <c r="E53">
-        <v>-2825.376</v>
+        <v>-2730.352000000001</v>
       </c>
       <c r="F53">
-        <v>4846.224</v>
+        <v>4941.248</v>
       </c>
       <c r="G53">
         <v>823.7</v>
@@ -5633,28 +5633,28 @@
         <v>1573.55</v>
       </c>
       <c r="M53">
-        <v>267.9961872</v>
+        <v>273.2510144</v>
       </c>
       <c r="N53">
-        <v>1305.5538128</v>
+        <v>1300.2989856</v>
       </c>
       <c r="O53">
-        <v>195.83307192</v>
+        <v>195.04484784</v>
       </c>
       <c r="P53">
-        <v>1109.72074088</v>
+        <v>1105.25413776</v>
       </c>
       <c r="Q53">
-        <v>2654.92074088</v>
+        <v>2650.45413776</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1228383804233383</v>
+        <v>0.1243156097898749</v>
       </c>
       <c r="T53">
-        <v>1.00406835279142</v>
+        <v>1.023321603555558</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.871538757473784</v>
+        <v>5.75862455059929</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08411409269913997</v>
+        <v>0.08406482899084419</v>
       </c>
       <c r="C54">
-        <v>5378.9961997222</v>
+        <v>5287.313991066815</v>
       </c>
       <c r="D54">
-        <v>9496.544199722199</v>
+        <v>9499.885991066814</v>
       </c>
       <c r="E54">
-        <v>-2730.352000000001</v>
+        <v>-2635.328</v>
       </c>
       <c r="F54">
-        <v>4941.248</v>
+        <v>5036.272</v>
       </c>
       <c r="G54">
         <v>823.7</v>
@@ -5715,28 +5715,28 @@
         <v>1573.55</v>
       </c>
       <c r="M54">
-        <v>273.2510144</v>
+        <v>278.5058416</v>
       </c>
       <c r="N54">
-        <v>1300.2989856</v>
+        <v>1295.0441584</v>
       </c>
       <c r="O54">
-        <v>195.04484784</v>
+        <v>194.25662376</v>
       </c>
       <c r="P54">
-        <v>1105.25413776</v>
+        <v>1100.78753464</v>
       </c>
       <c r="Q54">
-        <v>2650.45413776</v>
+        <v>2645.98753464</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1243156097898749</v>
+        <v>0.1258556999805195</v>
       </c>
       <c r="T54">
-        <v>1.023321603555558</v>
+        <v>1.043394141586255</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.75862455059929</v>
+        <v>5.649971257191756</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08406482899084419</v>
+        <v>0.08401556528254842</v>
       </c>
       <c r="C55">
-        <v>5287.313991066815</v>
+        <v>5195.634135162149</v>
       </c>
       <c r="D55">
-        <v>9499.885991066814</v>
+        <v>9503.230135162148</v>
       </c>
       <c r="E55">
-        <v>-2635.328</v>
+        <v>-2540.304</v>
       </c>
       <c r="F55">
-        <v>5036.272</v>
+        <v>5131.296</v>
       </c>
       <c r="G55">
         <v>823.7</v>
@@ -5797,28 +5797,28 @@
         <v>1573.55</v>
       </c>
       <c r="M55">
-        <v>278.5058416</v>
+        <v>283.7606688</v>
       </c>
       <c r="N55">
-        <v>1295.0441584</v>
+        <v>1289.7893312</v>
       </c>
       <c r="O55">
-        <v>194.25662376</v>
+        <v>193.46839968</v>
       </c>
       <c r="P55">
-        <v>1100.78753464</v>
+        <v>1096.32093152</v>
       </c>
       <c r="Q55">
-        <v>2645.98753464</v>
+        <v>2641.52093152</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1258556999805195</v>
+        <v>0.1274627506142357</v>
       </c>
       <c r="T55">
-        <v>1.043394141586255</v>
+        <v>1.064339398661765</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.649971257191756</v>
+        <v>5.545342159836352</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08401556528254842</v>
+        <v>0.08396630157425261</v>
       </c>
       <c r="C56">
-        <v>5195.634135162149</v>
+        <v>5103.95663449372</v>
       </c>
       <c r="D56">
-        <v>9503.230135162148</v>
+        <v>9506.57663449372</v>
       </c>
       <c r="E56">
-        <v>-2540.304</v>
+        <v>-2445.28</v>
       </c>
       <c r="F56">
-        <v>5131.296</v>
+        <v>5226.320000000001</v>
       </c>
       <c r="G56">
         <v>823.7</v>
@@ -5879,28 +5879,28 @@
         <v>1573.55</v>
       </c>
       <c r="M56">
-        <v>283.7606688</v>
+        <v>289.015496</v>
       </c>
       <c r="N56">
-        <v>1289.7893312</v>
+        <v>1284.534504</v>
       </c>
       <c r="O56">
-        <v>193.46839968</v>
+        <v>192.6801756</v>
       </c>
       <c r="P56">
-        <v>1096.32093152</v>
+        <v>1091.8543284</v>
       </c>
       <c r="Q56">
-        <v>2641.52093152</v>
+        <v>2637.0543284</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1274627506142357</v>
+        <v>0.1291412257205614</v>
       </c>
       <c r="T56">
-        <v>1.064339398661765</v>
+        <v>1.086215556051742</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.545342159836352</v>
+        <v>5.444517756930237</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08396630157425261</v>
+        <v>0.08391703786595683</v>
       </c>
       <c r="C57">
-        <v>5103.95663449372</v>
+        <v>5012.281491550543</v>
       </c>
       <c r="D57">
-        <v>9506.57663449372</v>
+        <v>9509.925491550543</v>
       </c>
       <c r="E57">
-        <v>-2445.28</v>
+        <v>-2350.256</v>
       </c>
       <c r="F57">
-        <v>5226.320000000001</v>
+        <v>5321.344</v>
       </c>
       <c r="G57">
         <v>823.7</v>
@@ -5961,28 +5961,28 @@
         <v>1573.55</v>
       </c>
       <c r="M57">
-        <v>289.015496</v>
+        <v>294.2703232</v>
       </c>
       <c r="N57">
-        <v>1284.534504</v>
+        <v>1279.2796768</v>
       </c>
       <c r="O57">
-        <v>192.6801756</v>
+        <v>191.89195152</v>
       </c>
       <c r="P57">
-        <v>1091.8543284</v>
+        <v>1087.38772528</v>
       </c>
       <c r="Q57">
-        <v>2637.0543284</v>
+        <v>2632.58772528</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1291412257205614</v>
+        <v>0.1308959951499019</v>
       </c>
       <c r="T57">
-        <v>1.086215556051742</v>
+        <v>1.109086084232172</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.444517756930237</v>
+        <v>5.347294225556483</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08391703786595683</v>
+        <v>0.08386777415766106</v>
       </c>
       <c r="C58">
-        <v>5012.281491550543</v>
+        <v>4920.608708825148</v>
       </c>
       <c r="D58">
-        <v>9509.925491550543</v>
+        <v>9513.276708825148</v>
       </c>
       <c r="E58">
-        <v>-2350.256</v>
+        <v>-2255.232</v>
       </c>
       <c r="F58">
-        <v>5321.344</v>
+        <v>5416.368</v>
       </c>
       <c r="G58">
         <v>823.7</v>
@@ -6043,28 +6043,28 @@
         <v>1573.55</v>
       </c>
       <c r="M58">
-        <v>294.2703232</v>
+        <v>299.5251504</v>
       </c>
       <c r="N58">
-        <v>1279.2796768</v>
+        <v>1274.0248496</v>
       </c>
       <c r="O58">
-        <v>191.89195152</v>
+        <v>191.10372744</v>
       </c>
       <c r="P58">
-        <v>1087.38772528</v>
+        <v>1082.92112216</v>
       </c>
       <c r="Q58">
-        <v>2632.58772528</v>
+        <v>2628.12112216</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1308959951499019</v>
+        <v>0.1327323817620025</v>
       </c>
       <c r="T58">
-        <v>1.109086084232172</v>
+        <v>1.133020357909367</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.347294225556483</v>
+        <v>5.253482046160754</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08386777415766106</v>
+        <v>0.08381851044936528</v>
       </c>
       <c r="C59">
-        <v>4920.608708825148</v>
+        <v>4828.938288813572</v>
       </c>
       <c r="D59">
-        <v>9513.276708825148</v>
+        <v>9516.630288813572</v>
       </c>
       <c r="E59">
-        <v>-2255.232</v>
+        <v>-2160.208</v>
       </c>
       <c r="F59">
-        <v>5416.368</v>
+        <v>5511.392000000001</v>
       </c>
       <c r="G59">
         <v>823.7</v>
@@ -6125,28 +6125,28 @@
         <v>1573.55</v>
       </c>
       <c r="M59">
-        <v>299.5251504</v>
+        <v>304.7799776000001</v>
       </c>
       <c r="N59">
-        <v>1274.0248496</v>
+        <v>1268.7700224</v>
       </c>
       <c r="O59">
-        <v>191.10372744</v>
+        <v>190.31550336</v>
       </c>
       <c r="P59">
-        <v>1082.92112216</v>
+        <v>1078.45451904</v>
       </c>
       <c r="Q59">
-        <v>2628.12112216</v>
+        <v>2623.65451904</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1327323817620025</v>
+        <v>0.1346562153556316</v>
       </c>
       <c r="T59">
-        <v>1.133020357909367</v>
+        <v>1.158094358904524</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.253482046160754</v>
+        <v>5.162904769502811</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08381851044936528</v>
+        <v>0.08376924674106949</v>
       </c>
       <c r="C60">
-        <v>4828.938288813573</v>
+        <v>4737.270234015386</v>
       </c>
       <c r="D60">
-        <v>9516.630288813572</v>
+        <v>9519.986234015385</v>
       </c>
       <c r="E60">
-        <v>-2160.208000000001</v>
+        <v>-2065.184000000001</v>
       </c>
       <c r="F60">
-        <v>5511.392</v>
+        <v>5606.415999999999</v>
       </c>
       <c r="G60">
         <v>823.7</v>
@@ -6207,28 +6207,28 @@
         <v>1573.55</v>
       </c>
       <c r="M60">
-        <v>304.7799776</v>
+        <v>310.0348048</v>
       </c>
       <c r="N60">
-        <v>1268.7700224</v>
+        <v>1263.5151952</v>
       </c>
       <c r="O60">
-        <v>190.31550336</v>
+        <v>189.52727928</v>
       </c>
       <c r="P60">
-        <v>1078.45451904</v>
+        <v>1073.98791592</v>
       </c>
       <c r="Q60">
-        <v>2623.65451904</v>
+        <v>2619.18791592</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1346562153556316</v>
+        <v>0.1366738944904134</v>
       </c>
       <c r="T60">
-        <v>1.158094358904523</v>
+        <v>1.184391481899443</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.162904769502812</v>
+        <v>5.075397909002764</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08376924674106949</v>
+        <v>0.08371998303277373</v>
       </c>
       <c r="C61">
-        <v>4737.270234015386</v>
+        <v>4645.60454693367</v>
       </c>
       <c r="D61">
-        <v>9519.986234015385</v>
+        <v>9523.344546933669</v>
       </c>
       <c r="E61">
-        <v>-2065.184000000001</v>
+        <v>-1970.160000000001</v>
       </c>
       <c r="F61">
-        <v>5606.415999999999</v>
+        <v>5701.44</v>
       </c>
       <c r="G61">
         <v>823.7</v>
@@ -6289,28 +6289,28 @@
         <v>1573.55</v>
       </c>
       <c r="M61">
-        <v>310.0348048</v>
+        <v>315.289632</v>
       </c>
       <c r="N61">
-        <v>1263.5151952</v>
+        <v>1258.260368</v>
       </c>
       <c r="O61">
-        <v>189.52727928</v>
+        <v>188.7390552</v>
       </c>
       <c r="P61">
-        <v>1073.98791592</v>
+        <v>1069.5213128</v>
       </c>
       <c r="Q61">
-        <v>2619.18791592</v>
+        <v>2614.7213128</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1366738944904134</v>
+        <v>0.1387924575819343</v>
       </c>
       <c r="T61">
-        <v>1.184391481899443</v>
+        <v>1.212003461044109</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.075397909002764</v>
+        <v>4.990807943852717</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08371998303277373</v>
+        <v>0.08367071932447794</v>
       </c>
       <c r="C62">
-        <v>4645.60454693367</v>
+        <v>4553.941230075057</v>
       </c>
       <c r="D62">
-        <v>9523.344546933669</v>
+        <v>9526.705230075057</v>
       </c>
       <c r="E62">
-        <v>-1970.160000000001</v>
+        <v>-1875.136</v>
       </c>
       <c r="F62">
-        <v>5701.44</v>
+        <v>5796.464</v>
       </c>
       <c r="G62">
         <v>823.7</v>
@@ -6371,28 +6371,28 @@
         <v>1573.55</v>
       </c>
       <c r="M62">
-        <v>315.289632</v>
+        <v>320.5444592</v>
       </c>
       <c r="N62">
-        <v>1258.260368</v>
+        <v>1253.0055408</v>
       </c>
       <c r="O62">
-        <v>188.7390552</v>
+        <v>187.95083112</v>
       </c>
       <c r="P62">
-        <v>1069.5213128</v>
+        <v>1065.05470968</v>
       </c>
       <c r="Q62">
-        <v>2614.7213128</v>
+        <v>2610.25470968</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1387924575819343</v>
+        <v>0.1410196649345588</v>
       </c>
       <c r="T62">
-        <v>1.212003461044109</v>
+        <v>1.241031439119271</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.990807943852717</v>
+        <v>4.908991420183</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08367071932447794</v>
+        <v>0.08362145561618216</v>
       </c>
       <c r="C63">
-        <v>4553.941230075057</v>
+        <v>4462.280285949701</v>
       </c>
       <c r="D63">
-        <v>9526.705230075057</v>
+        <v>9530.068285949699</v>
       </c>
       <c r="E63">
-        <v>-1875.136</v>
+        <v>-1780.112000000001</v>
       </c>
       <c r="F63">
-        <v>5796.464</v>
+        <v>5891.487999999999</v>
       </c>
       <c r="G63">
         <v>823.7</v>
@@ -6453,28 +6453,28 @@
         <v>1573.55</v>
       </c>
       <c r="M63">
-        <v>320.5444592</v>
+        <v>325.7992864</v>
       </c>
       <c r="N63">
-        <v>1253.0055408</v>
+        <v>1247.7507136</v>
       </c>
       <c r="O63">
-        <v>187.95083112</v>
+        <v>187.16260704</v>
       </c>
       <c r="P63">
-        <v>1065.05470968</v>
+        <v>1060.58810656</v>
       </c>
       <c r="Q63">
-        <v>2610.25470968</v>
+        <v>2605.78810656</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1410196649345588</v>
+        <v>0.1433640937267951</v>
       </c>
       <c r="T63">
-        <v>1.241031439119271</v>
+        <v>1.271587205514179</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.908991420183</v>
+        <v>4.829814139212307</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08362145561618216</v>
+        <v>0.08357219190788637</v>
       </c>
       <c r="C64">
-        <v>4462.280285949701</v>
+        <v>4370.621717071316</v>
       </c>
       <c r="D64">
-        <v>9530.068285949699</v>
+        <v>9533.433717071315</v>
       </c>
       <c r="E64">
-        <v>-1780.112000000001</v>
+        <v>-1685.088000000001</v>
       </c>
       <c r="F64">
-        <v>5891.487999999999</v>
+        <v>5986.512</v>
       </c>
       <c r="G64">
         <v>823.7</v>
@@ -6535,28 +6535,28 @@
         <v>1573.55</v>
       </c>
       <c r="M64">
-        <v>325.7992864</v>
+        <v>331.0541136</v>
       </c>
       <c r="N64">
-        <v>1247.7507136</v>
+        <v>1242.4958864</v>
       </c>
       <c r="O64">
-        <v>187.16260704</v>
+        <v>186.37438296</v>
       </c>
       <c r="P64">
-        <v>1060.58810656</v>
+        <v>1056.12150344</v>
       </c>
       <c r="Q64">
-        <v>2605.78810656</v>
+        <v>2601.32150344</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1433640937267951</v>
+        <v>0.1458352483996929</v>
       </c>
       <c r="T64">
-        <v>1.271587205514179</v>
+        <v>1.303794634957459</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.829814139212307</v>
+        <v>4.753150422716875</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08357219190788637</v>
+        <v>0.08352292819959059</v>
       </c>
       <c r="C65">
-        <v>4370.621717071316</v>
+        <v>4278.965525957157</v>
       </c>
       <c r="D65">
-        <v>9533.433717071315</v>
+        <v>9536.801525957157</v>
       </c>
       <c r="E65">
-        <v>-1685.088000000001</v>
+        <v>-1590.064</v>
       </c>
       <c r="F65">
-        <v>5986.512</v>
+        <v>6081.536</v>
       </c>
       <c r="G65">
         <v>823.7</v>
@@ -6617,28 +6617,28 @@
         <v>1573.55</v>
       </c>
       <c r="M65">
-        <v>331.0541136</v>
+        <v>336.3089408</v>
       </c>
       <c r="N65">
-        <v>1242.4958864</v>
+        <v>1237.2410592</v>
       </c>
       <c r="O65">
-        <v>186.37438296</v>
+        <v>185.58615888</v>
       </c>
       <c r="P65">
-        <v>1056.12150344</v>
+        <v>1051.65490032</v>
       </c>
       <c r="Q65">
-        <v>2601.32150344</v>
+        <v>2596.85490032</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1458352483996929</v>
+        <v>0.1484436894433072</v>
       </c>
       <c r="T65">
-        <v>1.303794634957459</v>
+        <v>1.337791366036478</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.753150422716875</v>
+        <v>4.678882447361922</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08352292819959059</v>
+        <v>0.08347366449129481</v>
       </c>
       <c r="C66">
-        <v>4278.965525957157</v>
+        <v>4187.311715128048</v>
       </c>
       <c r="D66">
-        <v>9536.801525957157</v>
+        <v>9540.171715128048</v>
       </c>
       <c r="E66">
-        <v>-1590.064</v>
+        <v>-1495.04</v>
       </c>
       <c r="F66">
-        <v>6081.536</v>
+        <v>6176.56</v>
       </c>
       <c r="G66">
         <v>823.7</v>
@@ -6699,28 +6699,28 @@
         <v>1573.55</v>
       </c>
       <c r="M66">
-        <v>336.3089408</v>
+        <v>341.563768</v>
       </c>
       <c r="N66">
-        <v>1237.2410592</v>
+        <v>1231.986232</v>
       </c>
       <c r="O66">
-        <v>185.58615888</v>
+        <v>184.7979348</v>
       </c>
       <c r="P66">
-        <v>1051.65490032</v>
+        <v>1047.1882972</v>
       </c>
       <c r="Q66">
-        <v>2596.85490032</v>
+        <v>2592.3882972</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1484436894433072</v>
+        <v>0.1512011842608423</v>
       </c>
       <c r="T66">
-        <v>1.337791366036478</v>
+        <v>1.373730767462868</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.678882447361922</v>
+        <v>4.606899640479432</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08347366449129481</v>
+        <v>0.08342440078299904</v>
       </c>
       <c r="C67">
-        <v>4187.311715128048</v>
+        <v>4095.66028710837</v>
       </c>
       <c r="D67">
-        <v>9540.171715128048</v>
+        <v>9543.544287108369</v>
       </c>
       <c r="E67">
-        <v>-1495.04</v>
+        <v>-1400.016000000001</v>
       </c>
       <c r="F67">
-        <v>6176.56</v>
+        <v>6271.584</v>
       </c>
       <c r="G67">
         <v>823.7</v>
@@ -6781,28 +6781,28 @@
         <v>1573.55</v>
       </c>
       <c r="M67">
-        <v>341.563768</v>
+        <v>346.8185952</v>
       </c>
       <c r="N67">
-        <v>1231.986232</v>
+        <v>1226.7314048</v>
       </c>
       <c r="O67">
-        <v>184.7979348</v>
+        <v>184.00971072</v>
       </c>
       <c r="P67">
-        <v>1047.1882972</v>
+        <v>1042.72169408</v>
       </c>
       <c r="Q67">
-        <v>2592.3882972</v>
+        <v>2587.92169408</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1512011842608423</v>
+        <v>0.1541208846558795</v>
       </c>
       <c r="T67">
-        <v>1.373730767462868</v>
+        <v>1.411784251326106</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.606899640479432</v>
+        <v>4.537098130775197</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08342440078299904</v>
+        <v>0.08479888707470326</v>
       </c>
       <c r="C68">
-        <v>4095.66028710837</v>
+        <v>3907.425647022917</v>
       </c>
       <c r="D68">
-        <v>9543.544287108369</v>
+        <v>9450.333647022917</v>
       </c>
       <c r="E68">
-        <v>-1400.016000000001</v>
+        <v>-1304.992</v>
       </c>
       <c r="F68">
-        <v>6271.584</v>
+        <v>6366.608</v>
       </c>
       <c r="G68">
         <v>823.7</v>
@@ -6863,45 +6863,45 @@
         <v>1573.55</v>
       </c>
       <c r="M68">
-        <v>346.8185952</v>
+        <v>367.9899424</v>
       </c>
       <c r="N68">
-        <v>1226.7314048</v>
+        <v>1205.5600576</v>
       </c>
       <c r="O68">
-        <v>184.00971072</v>
+        <v>180.83400864</v>
       </c>
       <c r="P68">
-        <v>1042.72169408</v>
+        <v>1024.72604896</v>
       </c>
       <c r="Q68">
-        <v>2587.92169408</v>
+        <v>2569.92604896</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1541208846558795</v>
+        <v>0.1572175365900099</v>
       </c>
       <c r="T68">
-        <v>1.411784251326106</v>
+        <v>1.45214400693863</v>
       </c>
       <c r="U68">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V68">
         <v>0.15</v>
       </c>
       <c r="W68">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>4.537098130775197</v>
+        <v>4.276067953752857</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08479888707470326</v>
+        <v>0.08477087336640748</v>
       </c>
       <c r="C69">
-        <v>3907.425647022917</v>
+        <v>3814.283213590389</v>
       </c>
       <c r="D69">
-        <v>9450.333647022917</v>
+        <v>9452.215213590389</v>
       </c>
       <c r="E69">
-        <v>-1304.992</v>
+        <v>-1209.968</v>
       </c>
       <c r="F69">
-        <v>6366.608</v>
+        <v>6461.632000000001</v>
       </c>
       <c r="G69">
         <v>823.7</v>
@@ -6945,28 +6945,28 @@
         <v>1573.55</v>
       </c>
       <c r="M69">
-        <v>367.9899424</v>
+        <v>373.4823296000001</v>
       </c>
       <c r="N69">
-        <v>1205.5600576</v>
+        <v>1200.0676704</v>
       </c>
       <c r="O69">
-        <v>180.83400864</v>
+        <v>180.01015056</v>
       </c>
       <c r="P69">
-        <v>1024.72604896</v>
+        <v>1020.05751984</v>
       </c>
       <c r="Q69">
-        <v>2569.92604896</v>
+        <v>2565.25751984</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1572175365900099</v>
+        <v>0.1605077292700234</v>
       </c>
       <c r="T69">
-        <v>1.45214400693863</v>
+        <v>1.495026247276938</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.276067953752857</v>
+        <v>4.213184601491785</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08477087336640748</v>
+        <v>0.08474285965811169</v>
       </c>
       <c r="C70">
-        <v>3814.283213590389</v>
+        <v>3721.141529548921</v>
       </c>
       <c r="D70">
-        <v>9452.215213590389</v>
+        <v>9454.097529548921</v>
       </c>
       <c r="E70">
-        <v>-1209.968</v>
+        <v>-1114.944</v>
       </c>
       <c r="F70">
-        <v>6461.632000000001</v>
+        <v>6556.656</v>
       </c>
       <c r="G70">
         <v>823.7</v>
@@ -7027,28 +7027,28 @@
         <v>1573.55</v>
       </c>
       <c r="M70">
-        <v>373.4823296000001</v>
+        <v>378.9747168</v>
       </c>
       <c r="N70">
-        <v>1200.0676704</v>
+        <v>1194.5752832</v>
       </c>
       <c r="O70">
-        <v>180.01015056</v>
+        <v>179.18629248</v>
       </c>
       <c r="P70">
-        <v>1020.05751984</v>
+        <v>1015.38899072</v>
       </c>
       <c r="Q70">
-        <v>2565.25751984</v>
+        <v>2560.58899072</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1605077292700234</v>
+        <v>0.1640101924455216</v>
       </c>
       <c r="T70">
-        <v>1.495026247276938</v>
+        <v>1.540675083766104</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.213184601491785</v>
+        <v>4.152123955093354</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08474285965811169</v>
+        <v>0.08471484594981592</v>
       </c>
       <c r="C71">
-        <v>3721.141529548921</v>
+        <v>3628.000595346299</v>
       </c>
       <c r="D71">
-        <v>9454.097529548921</v>
+        <v>9455.980595346298</v>
       </c>
       <c r="E71">
-        <v>-1114.944</v>
+        <v>-1019.92</v>
       </c>
       <c r="F71">
-        <v>6556.656</v>
+        <v>6651.68</v>
       </c>
       <c r="G71">
         <v>823.7</v>
@@ -7109,28 +7109,28 @@
         <v>1573.55</v>
       </c>
       <c r="M71">
-        <v>378.9747168</v>
+        <v>384.4671040000001</v>
       </c>
       <c r="N71">
-        <v>1194.5752832</v>
+        <v>1189.082896</v>
       </c>
       <c r="O71">
-        <v>179.18629248</v>
+        <v>178.3624344</v>
       </c>
       <c r="P71">
-        <v>1015.38899072</v>
+        <v>1010.7204616</v>
       </c>
       <c r="Q71">
-        <v>2560.58899072</v>
+        <v>2555.9204616</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1640101924455216</v>
+        <v>0.1677461531660531</v>
       </c>
       <c r="T71">
-        <v>1.540675083766104</v>
+        <v>1.589367176021214</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.152123955093354</v>
+        <v>4.092807898592021</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08471484594981592</v>
+        <v>0.08468683224152013</v>
       </c>
       <c r="C72">
-        <v>3628.000595346299</v>
+        <v>3534.860411430672</v>
       </c>
       <c r="D72">
-        <v>9455.980595346298</v>
+        <v>9457.864411430672</v>
       </c>
       <c r="E72">
-        <v>-1019.92</v>
+        <v>-924.8959999999997</v>
       </c>
       <c r="F72">
-        <v>6651.68</v>
+        <v>6746.704000000001</v>
       </c>
       <c r="G72">
         <v>823.7</v>
@@ -7191,28 +7191,28 @@
         <v>1573.55</v>
       </c>
       <c r="M72">
-        <v>384.4671040000001</v>
+        <v>389.9594912000001</v>
       </c>
       <c r="N72">
-        <v>1189.082896</v>
+        <v>1183.5905088</v>
       </c>
       <c r="O72">
-        <v>178.3624344</v>
+        <v>177.53857632</v>
       </c>
       <c r="P72">
-        <v>1010.7204616</v>
+        <v>1006.05193248</v>
       </c>
       <c r="Q72">
-        <v>2555.9204616</v>
+        <v>2551.25193248</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1677461531660531</v>
+        <v>0.1717397663500695</v>
       </c>
       <c r="T72">
-        <v>1.589367176021214</v>
+        <v>1.641417343604263</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.092807898592021</v>
+        <v>4.03516271692171</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08468683224152013</v>
+        <v>0.08680081853322436</v>
       </c>
       <c r="C73">
-        <v>3534.860411430673</v>
+        <v>3299.75640577939</v>
       </c>
       <c r="D73">
-        <v>9457.864411430672</v>
+        <v>9317.784405779388</v>
       </c>
       <c r="E73">
-        <v>-924.8960000000006</v>
+        <v>-829.8720000000012</v>
       </c>
       <c r="F73">
-        <v>6746.704</v>
+        <v>6841.727999999999</v>
       </c>
       <c r="G73">
         <v>823.7</v>
@@ -7273,45 +7273,45 @@
         <v>1573.55</v>
       </c>
       <c r="M73">
-        <v>389.9594912</v>
+        <v>419.3979264</v>
       </c>
       <c r="N73">
-        <v>1183.5905088</v>
+        <v>1154.1520736</v>
       </c>
       <c r="O73">
-        <v>177.53857632</v>
+        <v>173.12281104</v>
       </c>
       <c r="P73">
-        <v>1006.05193248</v>
+        <v>981.02926256</v>
       </c>
       <c r="Q73">
-        <v>2551.25193248</v>
+        <v>2526.22926256</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1717397663500694</v>
+        <v>0.1760186376186584</v>
       </c>
       <c r="T73">
-        <v>1.641417343604262</v>
+        <v>1.697185380300386</v>
       </c>
       <c r="U73">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V73">
         <v>0.15</v>
       </c>
       <c r="W73">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>4.035162716921711</v>
+        <v>3.751926037181285</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08680081853322436</v>
+        <v>0.08680255482492857</v>
       </c>
       <c r="C74">
-        <v>3299.75640577939</v>
+        <v>3204.619058535375</v>
       </c>
       <c r="D74">
-        <v>9317.784405779388</v>
+        <v>9317.671058535374</v>
       </c>
       <c r="E74">
-        <v>-829.8720000000012</v>
+        <v>-734.8480000000009</v>
       </c>
       <c r="F74">
-        <v>6841.727999999999</v>
+        <v>6936.751999999999</v>
       </c>
       <c r="G74">
         <v>823.7</v>
@@ -7355,28 +7355,28 @@
         <v>1573.55</v>
       </c>
       <c r="M74">
-        <v>419.3979264</v>
+        <v>425.2228976</v>
       </c>
       <c r="N74">
-        <v>1154.1520736</v>
+        <v>1148.3271024</v>
       </c>
       <c r="O74">
-        <v>173.12281104</v>
+        <v>172.24906536</v>
       </c>
       <c r="P74">
-        <v>981.02926256</v>
+        <v>976.07803704</v>
       </c>
       <c r="Q74">
-        <v>2526.22926256</v>
+        <v>2521.27803704</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1760186376186584</v>
+        <v>0.1806144623145503</v>
       </c>
       <c r="T74">
-        <v>1.697185380300386</v>
+        <v>1.757084382677704</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.751926037181285</v>
+        <v>3.70052979009661</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08680255482492857</v>
+        <v>0.08680429111663279</v>
       </c>
       <c r="C75">
-        <v>3204.619058535375</v>
+        <v>3109.481714048976</v>
       </c>
       <c r="D75">
-        <v>9317.671058535374</v>
+        <v>9317.557714048975</v>
       </c>
       <c r="E75">
-        <v>-734.8480000000009</v>
+        <v>-639.8240000000005</v>
       </c>
       <c r="F75">
-        <v>6936.751999999999</v>
+        <v>7031.776</v>
       </c>
       <c r="G75">
         <v>823.7</v>
@@ -7437,28 +7437,28 @@
         <v>1573.55</v>
       </c>
       <c r="M75">
-        <v>425.2228976</v>
+        <v>431.0478688</v>
       </c>
       <c r="N75">
-        <v>1148.3271024</v>
+        <v>1142.5021312</v>
       </c>
       <c r="O75">
-        <v>172.24906536</v>
+        <v>171.37531968</v>
       </c>
       <c r="P75">
-        <v>976.07803704</v>
+        <v>971.1268115199999</v>
       </c>
       <c r="Q75">
-        <v>2521.27803704</v>
+        <v>2516.32681152</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1806144623145503</v>
+        <v>0.1855638119870492</v>
       </c>
       <c r="T75">
-        <v>1.757084382677704</v>
+        <v>1.821591000622508</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.70052979009661</v>
+        <v>3.650522630770979</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08680429111663279</v>
+        <v>0.08680602740833701</v>
       </c>
       <c r="C76">
-        <v>3109.481714048976</v>
+        <v>3014.344372320096</v>
       </c>
       <c r="D76">
-        <v>9317.557714048975</v>
+        <v>9317.444372320095</v>
       </c>
       <c r="E76">
-        <v>-639.8240000000005</v>
+        <v>-544.8000000000011</v>
       </c>
       <c r="F76">
-        <v>7031.776</v>
+        <v>7126.799999999999</v>
       </c>
       <c r="G76">
         <v>823.7</v>
@@ -7519,28 +7519,28 @@
         <v>1573.55</v>
       </c>
       <c r="M76">
-        <v>431.0478688</v>
+        <v>436.8728399999999</v>
       </c>
       <c r="N76">
-        <v>1142.5021312</v>
+        <v>1136.67716</v>
       </c>
       <c r="O76">
-        <v>171.37531968</v>
+        <v>170.501574</v>
       </c>
       <c r="P76">
-        <v>971.1268115199999</v>
+        <v>966.175586</v>
       </c>
       <c r="Q76">
-        <v>2516.32681152</v>
+        <v>2511.375586</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1855638119870492</v>
+        <v>0.190909109633348</v>
       </c>
       <c r="T76">
-        <v>1.821591000622508</v>
+        <v>1.891258148002896</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.650522630770979</v>
+        <v>3.601848995694033</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08680602740833701</v>
+        <v>0.08680776370004123</v>
       </c>
       <c r="C77">
-        <v>3014.344372320096</v>
+        <v>2919.207033348631</v>
       </c>
       <c r="D77">
-        <v>9317.444372320095</v>
+        <v>9317.33103334863</v>
       </c>
       <c r="E77">
-        <v>-544.8000000000011</v>
+        <v>-449.7760000000007</v>
       </c>
       <c r="F77">
-        <v>7126.799999999999</v>
+        <v>7221.824</v>
       </c>
       <c r="G77">
         <v>823.7</v>
@@ -7601,28 +7601,28 @@
         <v>1573.55</v>
       </c>
       <c r="M77">
-        <v>436.8728399999999</v>
+        <v>442.6978112</v>
       </c>
       <c r="N77">
-        <v>1136.67716</v>
+        <v>1130.8521888</v>
       </c>
       <c r="O77">
-        <v>170.501574</v>
+        <v>169.62782832</v>
       </c>
       <c r="P77">
-        <v>966.175586</v>
+        <v>961.2243604800001</v>
       </c>
       <c r="Q77">
-        <v>2511.375586</v>
+        <v>2506.42436048</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.190909109633348</v>
+        <v>0.1966998487501718</v>
       </c>
       <c r="T77">
-        <v>1.891258148002896</v>
+        <v>1.966730890998317</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.601848995694033</v>
+        <v>3.554456245750691</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08680776370004123</v>
+        <v>0.08680949999174543</v>
       </c>
       <c r="C78">
-        <v>2919.207033348631</v>
+        <v>2824.069697134481</v>
       </c>
       <c r="D78">
-        <v>9317.33103334863</v>
+        <v>9317.21769713448</v>
       </c>
       <c r="E78">
-        <v>-449.7760000000007</v>
+        <v>-354.7520000000004</v>
       </c>
       <c r="F78">
-        <v>7221.824</v>
+        <v>7316.848</v>
       </c>
       <c r="G78">
         <v>823.7</v>
@@ -7683,28 +7683,28 @@
         <v>1573.55</v>
       </c>
       <c r="M78">
-        <v>442.6978112</v>
+        <v>448.5227824</v>
       </c>
       <c r="N78">
-        <v>1130.8521888</v>
+        <v>1125.0272176</v>
       </c>
       <c r="O78">
-        <v>169.62782832</v>
+        <v>168.75408264</v>
       </c>
       <c r="P78">
-        <v>961.2243604800001</v>
+        <v>956.2731349599999</v>
       </c>
       <c r="Q78">
-        <v>2506.42436048</v>
+        <v>2501.47313496</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1966998487501718</v>
+        <v>0.2029941303988932</v>
       </c>
       <c r="T78">
-        <v>1.966730890998317</v>
+        <v>2.048766481210731</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.554456245750691</v>
+        <v>3.508294476325357</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08680949999174543</v>
+        <v>0.08866763628344967</v>
       </c>
       <c r="C79">
-        <v>2824.069697134481</v>
+        <v>2609.316164045172</v>
       </c>
       <c r="D79">
-        <v>9317.21769713448</v>
+        <v>9197.488164045171</v>
       </c>
       <c r="E79">
-        <v>-354.7520000000004</v>
+        <v>-259.7280000000001</v>
       </c>
       <c r="F79">
-        <v>7316.848</v>
+        <v>7411.872</v>
       </c>
       <c r="G79">
         <v>823.7</v>
@@ -7765,45 +7765,45 @@
         <v>1573.55</v>
       </c>
       <c r="M79">
-        <v>448.5227824</v>
+        <v>475.1009952000001</v>
       </c>
       <c r="N79">
-        <v>1125.0272176</v>
+        <v>1098.4490048</v>
       </c>
       <c r="O79">
-        <v>168.75408264</v>
+        <v>164.76735072</v>
       </c>
       <c r="P79">
-        <v>956.2731349599999</v>
+        <v>933.6816540799998</v>
       </c>
       <c r="Q79">
-        <v>2501.47313496</v>
+        <v>2478.88165408</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2029941303988932</v>
+        <v>0.2098606194702258</v>
       </c>
       <c r="T79">
-        <v>2.048766481210731</v>
+        <v>2.138259852351546</v>
       </c>
       <c r="U79">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V79">
         <v>0.15</v>
       </c>
       <c r="W79">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y79">
-        <v>3.508294476325357</v>
+        <v>3.312032632845976</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08866763628344967</v>
+        <v>0.08869317257515388</v>
       </c>
       <c r="C80">
-        <v>2609.316164045172</v>
+        <v>2512.668157190027</v>
       </c>
       <c r="D80">
-        <v>9197.488164045171</v>
+        <v>9195.864157190026</v>
       </c>
       <c r="E80">
-        <v>-259.7280000000001</v>
+        <v>-164.7040000000006</v>
       </c>
       <c r="F80">
-        <v>7411.872</v>
+        <v>7506.896</v>
       </c>
       <c r="G80">
         <v>823.7</v>
@@ -7847,28 +7847,28 @@
         <v>1573.55</v>
       </c>
       <c r="M80">
-        <v>475.1009952000001</v>
+        <v>481.1920336</v>
       </c>
       <c r="N80">
-        <v>1098.4490048</v>
+        <v>1092.3579664</v>
       </c>
       <c r="O80">
-        <v>164.76735072</v>
+        <v>163.85369496</v>
       </c>
       <c r="P80">
-        <v>933.6816540799998</v>
+        <v>928.5042714399999</v>
       </c>
       <c r="Q80">
-        <v>2478.88165408</v>
+        <v>2473.70427144</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2098606194702258</v>
+        <v>0.2173810598816852</v>
       </c>
       <c r="T80">
-        <v>2.138259852351546</v>
+        <v>2.236276401696248</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.312032632845976</v>
+        <v>3.270108169139066</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08869317257515388</v>
+        <v>0.08871870886685809</v>
       </c>
       <c r="C81">
-        <v>2512.668157190027</v>
+        <v>2416.020723737662</v>
       </c>
       <c r="D81">
-        <v>9195.864157190026</v>
+        <v>9194.240723737661</v>
       </c>
       <c r="E81">
-        <v>-164.7040000000006</v>
+        <v>-69.68000000000029</v>
       </c>
       <c r="F81">
-        <v>7506.896</v>
+        <v>7601.92</v>
       </c>
       <c r="G81">
         <v>823.7</v>
@@ -7929,28 +7929,28 @@
         <v>1573.55</v>
       </c>
       <c r="M81">
-        <v>481.1920336</v>
+        <v>487.2830720000001</v>
       </c>
       <c r="N81">
-        <v>1092.3579664</v>
+        <v>1086.266928</v>
       </c>
       <c r="O81">
-        <v>163.85369496</v>
+        <v>162.9400392</v>
       </c>
       <c r="P81">
-        <v>928.5042714399999</v>
+        <v>923.3268888</v>
       </c>
       <c r="Q81">
-        <v>2473.70427144</v>
+        <v>2468.5268888</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2173810598816852</v>
+        <v>0.2256535443342905</v>
       </c>
       <c r="T81">
-        <v>2.236276401696248</v>
+        <v>2.344094605975421</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.270108169139066</v>
+        <v>3.229231817024828</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08871870886685809</v>
+        <v>0.08874424515856233</v>
       </c>
       <c r="C82">
-        <v>2416.020723737662</v>
+        <v>2319.37386338445</v>
       </c>
       <c r="D82">
-        <v>9194.240723737661</v>
+        <v>9192.61786338445</v>
       </c>
       <c r="E82">
-        <v>-69.68000000000029</v>
+        <v>25.34400000000005</v>
       </c>
       <c r="F82">
-        <v>7601.92</v>
+        <v>7696.944</v>
       </c>
       <c r="G82">
         <v>823.7</v>
@@ -8011,28 +8011,28 @@
         <v>1573.55</v>
       </c>
       <c r="M82">
-        <v>487.2830720000001</v>
+        <v>493.3741104000001</v>
       </c>
       <c r="N82">
-        <v>1086.266928</v>
+        <v>1080.1758896</v>
       </c>
       <c r="O82">
-        <v>162.9400392</v>
+        <v>162.02638344</v>
       </c>
       <c r="P82">
-        <v>923.3268888</v>
+        <v>918.1495061599999</v>
       </c>
       <c r="Q82">
-        <v>2468.5268888</v>
+        <v>2463.34950616</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2256535443342905</v>
+        <v>0.2347968166240123</v>
       </c>
       <c r="T82">
-        <v>2.344094605975421</v>
+        <v>2.46326209491556</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.229231817024828</v>
+        <v>3.189364757555385</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08874424515856233</v>
+        <v>0.08876978145026654</v>
       </c>
       <c r="C83">
-        <v>2319.37386338445</v>
+        <v>2222.727575826978</v>
       </c>
       <c r="D83">
-        <v>9192.61786338445</v>
+        <v>9190.995575826977</v>
       </c>
       <c r="E83">
-        <v>25.34400000000005</v>
+        <v>120.3679999999995</v>
       </c>
       <c r="F83">
-        <v>7696.944</v>
+        <v>7791.968</v>
       </c>
       <c r="G83">
         <v>823.7</v>
@@ -8093,28 +8093,28 @@
         <v>1573.55</v>
       </c>
       <c r="M83">
-        <v>493.3741104000001</v>
+        <v>499.4651488</v>
       </c>
       <c r="N83">
-        <v>1080.1758896</v>
+        <v>1074.0848512</v>
       </c>
       <c r="O83">
-        <v>162.02638344</v>
+        <v>161.11272768</v>
       </c>
       <c r="P83">
-        <v>918.1495061599999</v>
+        <v>912.97212352</v>
       </c>
       <c r="Q83">
-        <v>2463.34950616</v>
+        <v>2458.17212352</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2347968166240123</v>
+        <v>0.2449560080570364</v>
       </c>
       <c r="T83">
-        <v>2.46326209491556</v>
+        <v>2.595670415960158</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.189364757555385</v>
+        <v>3.150470065390076</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08876978145026654</v>
+        <v>0.08879531774197075</v>
       </c>
       <c r="C84">
-        <v>2222.727575826978</v>
+        <v>2126.081860762039</v>
       </c>
       <c r="D84">
-        <v>9190.995575826977</v>
+        <v>9189.373860762038</v>
       </c>
       <c r="E84">
-        <v>120.3679999999995</v>
+        <v>215.3919999999998</v>
       </c>
       <c r="F84">
-        <v>7791.968</v>
+        <v>7886.992</v>
       </c>
       <c r="G84">
         <v>823.7</v>
@@ -8175,28 +8175,28 @@
         <v>1573.55</v>
       </c>
       <c r="M84">
-        <v>499.4651488</v>
+        <v>505.5561872000001</v>
       </c>
       <c r="N84">
-        <v>1074.0848512</v>
+        <v>1067.9938128</v>
       </c>
       <c r="O84">
-        <v>161.11272768</v>
+        <v>160.19907192</v>
       </c>
       <c r="P84">
-        <v>912.97212352</v>
+        <v>907.7947408799999</v>
       </c>
       <c r="Q84">
-        <v>2458.17212352</v>
+        <v>2452.99474088</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2449560080570364</v>
+        <v>0.256310398482181</v>
       </c>
       <c r="T84">
-        <v>2.595670415960158</v>
+        <v>2.743656186539414</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.150470065390076</v>
+        <v>3.112512594722725</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08879531774197075</v>
+        <v>0.08882085403367498</v>
       </c>
       <c r="C85">
-        <v>2126.081860762039</v>
+        <v>2029.436717886642</v>
       </c>
       <c r="D85">
-        <v>9189.373860762038</v>
+        <v>9187.752717886642</v>
       </c>
       <c r="E85">
-        <v>215.3919999999998</v>
+        <v>310.4160000000002</v>
       </c>
       <c r="F85">
-        <v>7886.992</v>
+        <v>7982.016000000001</v>
       </c>
       <c r="G85">
         <v>823.7</v>
@@ -8257,28 +8257,28 @@
         <v>1573.55</v>
       </c>
       <c r="M85">
-        <v>505.5561872000001</v>
+        <v>511.6472256000001</v>
       </c>
       <c r="N85">
-        <v>1067.9938128</v>
+        <v>1061.9027744</v>
       </c>
       <c r="O85">
-        <v>160.19907192</v>
+        <v>159.28541616</v>
       </c>
       <c r="P85">
-        <v>907.7947408799999</v>
+        <v>902.61735824</v>
       </c>
       <c r="Q85">
-        <v>2452.99474088</v>
+        <v>2447.81735824</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.256310398482181</v>
+        <v>0.2690840877104687</v>
       </c>
       <c r="T85">
-        <v>2.743656186539414</v>
+        <v>2.910140178441078</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.112512594722725</v>
+        <v>3.075458873356979</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08882085403367498</v>
+        <v>0.08884639032537919</v>
       </c>
       <c r="C86">
-        <v>2029.436717886643</v>
+        <v>1932.792146898017</v>
       </c>
       <c r="D86">
-        <v>9187.752717886642</v>
+        <v>9186.132146898015</v>
       </c>
       <c r="E86">
-        <v>310.4159999999993</v>
+        <v>405.4399999999987</v>
       </c>
       <c r="F86">
-        <v>7982.016</v>
+        <v>8077.039999999999</v>
       </c>
       <c r="G86">
         <v>823.7</v>
@@ -8339,28 +8339,28 @@
         <v>1573.55</v>
       </c>
       <c r="M86">
-        <v>511.6472256</v>
+        <v>517.738264</v>
       </c>
       <c r="N86">
-        <v>1061.9027744</v>
+        <v>1055.811736</v>
       </c>
       <c r="O86">
-        <v>159.28541616</v>
+        <v>158.3717604</v>
       </c>
       <c r="P86">
-        <v>902.61735824</v>
+        <v>897.4399756000001</v>
       </c>
       <c r="Q86">
-        <v>2447.81735824</v>
+        <v>2442.6399756</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2690840877104686</v>
+        <v>0.283560935502528</v>
       </c>
       <c r="T86">
-        <v>2.910140178441076</v>
+        <v>3.098822035929628</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.075458873356979</v>
+        <v>3.039277004258662</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08884639032537919</v>
+        <v>0.08887192661708342</v>
       </c>
       <c r="C87">
-        <v>1932.792146898017</v>
+        <v>1836.1481474936</v>
       </c>
       <c r="D87">
-        <v>9186.132146898015</v>
+        <v>9184.512147493599</v>
       </c>
       <c r="E87">
-        <v>405.4399999999987</v>
+        <v>500.463999999999</v>
       </c>
       <c r="F87">
-        <v>8077.039999999999</v>
+        <v>8172.063999999999</v>
       </c>
       <c r="G87">
         <v>823.7</v>
@@ -8421,28 +8421,28 @@
         <v>1573.55</v>
       </c>
       <c r="M87">
-        <v>517.738264</v>
+        <v>523.8293024</v>
       </c>
       <c r="N87">
-        <v>1055.811736</v>
+        <v>1049.7206976</v>
       </c>
       <c r="O87">
-        <v>158.3717604</v>
+        <v>157.45810464</v>
       </c>
       <c r="P87">
-        <v>897.4399756000001</v>
+        <v>892.26259296</v>
       </c>
       <c r="Q87">
-        <v>2442.6399756</v>
+        <v>2437.46259296</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.283560935502528</v>
+        <v>0.3001059044077387</v>
       </c>
       <c r="T87">
-        <v>3.098822035929628</v>
+        <v>3.314458444487973</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.039277004258662</v>
+        <v>3.003936573976584</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08887192661708342</v>
+        <v>0.09466556290878764</v>
       </c>
       <c r="C88">
-        <v>1836.1481474936</v>
+        <v>1387.783279640375</v>
       </c>
       <c r="D88">
-        <v>9184.512147493599</v>
+        <v>8831.171279640374</v>
       </c>
       <c r="E88">
-        <v>500.463999999999</v>
+        <v>595.4879999999994</v>
       </c>
       <c r="F88">
-        <v>8172.063999999999</v>
+        <v>8267.088</v>
       </c>
       <c r="G88">
         <v>823.7</v>
@@ -8503,45 +8503,45 @@
         <v>1573.55</v>
       </c>
       <c r="M88">
-        <v>523.8293024</v>
+        <v>594.4036272000001</v>
       </c>
       <c r="N88">
-        <v>1049.7206976</v>
+        <v>979.1463727999999</v>
       </c>
       <c r="O88">
-        <v>157.45810464</v>
+        <v>146.87195592</v>
       </c>
       <c r="P88">
-        <v>892.26259296</v>
+        <v>832.2744168799999</v>
       </c>
       <c r="Q88">
-        <v>2437.46259296</v>
+        <v>2377.47441688</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3001059044077387</v>
+        <v>0.3191962531445203</v>
       </c>
       <c r="T88">
-        <v>3.314458444487973</v>
+        <v>3.563269685132217</v>
       </c>
       <c r="U88">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V88">
         <v>0.15</v>
       </c>
       <c r="W88">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y88">
-        <v>3.003936573976584</v>
+        <v>2.647275231835933</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09466556290878764</v>
+        <v>0.09475739920049187</v>
       </c>
       <c r="C89">
-        <v>1387.783279640375</v>
+        <v>1287.377146497705</v>
       </c>
       <c r="D89">
-        <v>8831.171279640374</v>
+        <v>8825.789146497704</v>
       </c>
       <c r="E89">
-        <v>595.4879999999994</v>
+        <v>690.5119999999988</v>
       </c>
       <c r="F89">
-        <v>8267.088</v>
+        <v>8362.111999999999</v>
       </c>
       <c r="G89">
         <v>823.7</v>
@@ -8585,28 +8585,28 @@
         <v>1573.55</v>
       </c>
       <c r="M89">
-        <v>594.4036272000001</v>
+        <v>601.2358528</v>
       </c>
       <c r="N89">
-        <v>979.1463727999999</v>
+        <v>972.3141472</v>
       </c>
       <c r="O89">
-        <v>146.87195592</v>
+        <v>145.84712208</v>
       </c>
       <c r="P89">
-        <v>832.2744168799999</v>
+        <v>826.46702512</v>
       </c>
       <c r="Q89">
-        <v>2377.47441688</v>
+        <v>2371.66702512</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3191962531445203</v>
+        <v>0.3414683266707655</v>
       </c>
       <c r="T89">
-        <v>3.563269685132217</v>
+        <v>3.853549465883836</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.647275231835933</v>
+        <v>2.617192558746889</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09475739920049187</v>
+        <v>0.09484923549219608</v>
       </c>
       <c r="C90">
-        <v>1287.377146497705</v>
+        <v>1186.977569611943</v>
       </c>
       <c r="D90">
-        <v>8825.789146497704</v>
+        <v>8820.413569611943</v>
       </c>
       <c r="E90">
-        <v>690.5119999999988</v>
+        <v>785.5360000000001</v>
       </c>
       <c r="F90">
-        <v>8362.111999999999</v>
+        <v>8457.136</v>
       </c>
       <c r="G90">
         <v>823.7</v>
@@ -8667,28 +8667,28 @@
         <v>1573.55</v>
       </c>
       <c r="M90">
-        <v>601.2358528</v>
+        <v>608.0680784000001</v>
       </c>
       <c r="N90">
-        <v>972.3141472</v>
+        <v>965.4819215999999</v>
       </c>
       <c r="O90">
-        <v>145.84712208</v>
+        <v>144.82228824</v>
       </c>
       <c r="P90">
-        <v>826.46702512</v>
+        <v>820.6596333599998</v>
       </c>
       <c r="Q90">
-        <v>2371.66702512</v>
+        <v>2365.85963336</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3414683266707655</v>
+        <v>0.3677898681108734</v>
       </c>
       <c r="T90">
-        <v>3.853549465883836</v>
+        <v>4.196607388590294</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.617192558746889</v>
+        <v>2.587785900783441</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09484923549219608</v>
+        <v>0.09494107178390029</v>
       </c>
       <c r="C91">
-        <v>1186.977569611943</v>
+        <v>1086.5845370106</v>
       </c>
       <c r="D91">
-        <v>8820.413569611943</v>
+        <v>8815.044537010599</v>
       </c>
       <c r="E91">
-        <v>785.5360000000001</v>
+        <v>880.5599999999995</v>
       </c>
       <c r="F91">
-        <v>8457.136</v>
+        <v>8552.16</v>
       </c>
       <c r="G91">
         <v>823.7</v>
@@ -8749,28 +8749,28 @@
         <v>1573.55</v>
       </c>
       <c r="M91">
-        <v>608.0680784000001</v>
+        <v>614.900304</v>
       </c>
       <c r="N91">
-        <v>965.4819215999999</v>
+        <v>958.6496959999999</v>
       </c>
       <c r="O91">
-        <v>144.82228824</v>
+        <v>143.7974544</v>
       </c>
       <c r="P91">
-        <v>820.6596333599998</v>
+        <v>814.8522416</v>
       </c>
       <c r="Q91">
-        <v>2365.85963336</v>
+        <v>2360.0522416</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3677898681108734</v>
+        <v>0.3993757178390031</v>
       </c>
       <c r="T91">
-        <v>4.196607388590294</v>
+        <v>4.608276895838045</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.587785900783441</v>
+        <v>2.559032724108069</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09494107178390029</v>
+        <v>0.09503290807560452</v>
       </c>
       <c r="C92">
-        <v>1086.5845370106</v>
+        <v>986.1980367503256</v>
       </c>
       <c r="D92">
-        <v>8815.044537010599</v>
+        <v>8809.682036750324</v>
       </c>
       <c r="E92">
-        <v>880.5599999999995</v>
+        <v>975.5839999999989</v>
       </c>
       <c r="F92">
-        <v>8552.16</v>
+        <v>8647.183999999999</v>
       </c>
       <c r="G92">
         <v>823.7</v>
@@ -8831,28 +8831,28 @@
         <v>1573.55</v>
       </c>
       <c r="M92">
-        <v>614.900304</v>
+        <v>621.7325296</v>
       </c>
       <c r="N92">
-        <v>958.6496959999999</v>
+        <v>951.8174703999999</v>
       </c>
       <c r="O92">
-        <v>143.7974544</v>
+        <v>142.77262056</v>
       </c>
       <c r="P92">
-        <v>814.8522416</v>
+        <v>809.04484984</v>
       </c>
       <c r="Q92">
-        <v>2360.0522416</v>
+        <v>2354.24484984</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3993757178390031</v>
+        <v>0.4379806452844947</v>
       </c>
       <c r="T92">
-        <v>4.608276895838045</v>
+        <v>5.111428515807517</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.559032724108069</v>
+        <v>2.530911485381607</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09503290807560452</v>
+        <v>0.09512474436730874</v>
       </c>
       <c r="C93">
-        <v>986.1980367503256</v>
+        <v>885.8180569168107</v>
       </c>
       <c r="D93">
-        <v>8809.682036750324</v>
+        <v>8804.326056916811</v>
       </c>
       <c r="E93">
-        <v>975.5839999999989</v>
+        <v>1070.608</v>
       </c>
       <c r="F93">
-        <v>8647.183999999999</v>
+        <v>8742.208000000001</v>
       </c>
       <c r="G93">
         <v>823.7</v>
@@ -8913,28 +8913,28 @@
         <v>1573.55</v>
       </c>
       <c r="M93">
-        <v>621.7325296</v>
+        <v>628.5647552</v>
       </c>
       <c r="N93">
-        <v>951.8174703999999</v>
+        <v>944.9852447999999</v>
       </c>
       <c r="O93">
-        <v>142.77262056</v>
+        <v>141.74778672</v>
       </c>
       <c r="P93">
-        <v>809.04484984</v>
+        <v>803.2374580799999</v>
       </c>
       <c r="Q93">
-        <v>2354.24484984</v>
+        <v>2348.43745808</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4379806452844947</v>
+        <v>0.4862368045913594</v>
       </c>
       <c r="T93">
-        <v>5.111428515807517</v>
+        <v>5.740368040769358</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.530911485381607</v>
+        <v>2.503401577931807</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09512474436730874</v>
+        <v>0.09829953065901295</v>
       </c>
       <c r="C94">
-        <v>885.8180569168107</v>
+        <v>609.5591563415182</v>
       </c>
       <c r="D94">
-        <v>8804.326056916811</v>
+        <v>8623.091156341517</v>
       </c>
       <c r="E94">
-        <v>1070.608</v>
+        <v>1165.632</v>
       </c>
       <c r="F94">
-        <v>8742.208000000001</v>
+        <v>8837.232</v>
       </c>
       <c r="G94">
         <v>823.7</v>
@@ -8995,45 +8995,45 @@
         <v>1573.55</v>
       </c>
       <c r="M94">
-        <v>628.5647552</v>
+        <v>669.8621856000001</v>
       </c>
       <c r="N94">
-        <v>944.9852447999999</v>
+        <v>903.6878143999999</v>
       </c>
       <c r="O94">
-        <v>141.74778672</v>
+        <v>135.55317216</v>
       </c>
       <c r="P94">
-        <v>803.2374580799999</v>
+        <v>768.1346422399999</v>
       </c>
       <c r="Q94">
-        <v>2348.43745808</v>
+        <v>2313.33464224</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4862368045913594</v>
+        <v>0.5482804379858996</v>
       </c>
       <c r="T94">
-        <v>5.740368040769358</v>
+        <v>6.549004572863153</v>
       </c>
       <c r="U94">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V94">
         <v>0.15</v>
       </c>
       <c r="W94">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y94">
-        <v>2.503401577931807</v>
+        <v>2.349065276151632</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09829953065901295</v>
+        <v>0.09842451695071716</v>
       </c>
       <c r="C95">
-        <v>609.5591563415182</v>
+        <v>507.5527555339795</v>
       </c>
       <c r="D95">
-        <v>8623.091156341517</v>
+        <v>8616.108755533978</v>
       </c>
       <c r="E95">
-        <v>1165.632</v>
+        <v>1260.655999999999</v>
       </c>
       <c r="F95">
-        <v>8837.232</v>
+        <v>8932.255999999999</v>
       </c>
       <c r="G95">
         <v>823.7</v>
@@ -9077,28 +9077,28 @@
         <v>1573.55</v>
       </c>
       <c r="M95">
-        <v>669.8621856000001</v>
+        <v>677.0650048</v>
       </c>
       <c r="N95">
-        <v>903.6878143999999</v>
+        <v>896.4849952</v>
       </c>
       <c r="O95">
-        <v>135.55317216</v>
+        <v>134.47274928</v>
       </c>
       <c r="P95">
-        <v>768.1346422399999</v>
+        <v>762.0122459199999</v>
       </c>
       <c r="Q95">
-        <v>2313.33464224</v>
+        <v>2307.21224592</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5482804379858996</v>
+        <v>0.6310052825119533</v>
       </c>
       <c r="T95">
-        <v>6.549004572863153</v>
+        <v>7.62718661565488</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.349065276151632</v>
+        <v>2.32407522002236</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09842451695071716</v>
+        <v>0.0985495032424214</v>
       </c>
       <c r="C96">
-        <v>507.5527555339795</v>
+        <v>405.5576533372096</v>
       </c>
       <c r="D96">
-        <v>8616.108755533978</v>
+        <v>8609.137653337209</v>
       </c>
       <c r="E96">
-        <v>1260.655999999999</v>
+        <v>1355.68</v>
       </c>
       <c r="F96">
-        <v>8932.255999999999</v>
+        <v>9027.280000000001</v>
       </c>
       <c r="G96">
         <v>823.7</v>
@@ -9159,28 +9159,28 @@
         <v>1573.55</v>
       </c>
       <c r="M96">
-        <v>677.0650048</v>
+        <v>684.2678240000001</v>
       </c>
       <c r="N96">
-        <v>896.4849952</v>
+        <v>889.2821759999998</v>
       </c>
       <c r="O96">
-        <v>134.47274928</v>
+        <v>133.3923264</v>
       </c>
       <c r="P96">
-        <v>762.0122459199999</v>
+        <v>755.8898495999998</v>
       </c>
       <c r="Q96">
-        <v>2307.21224592</v>
+        <v>2301.0898496</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6310052825119533</v>
+        <v>0.7468200648484288</v>
       </c>
       <c r="T96">
-        <v>7.62718661565488</v>
+        <v>9.136641475563302</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.32407522002236</v>
+        <v>2.299611270337913</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.0985495032424214</v>
+        <v>0.09867448953412561</v>
       </c>
       <c r="C97">
-        <v>405.5576533372096</v>
+        <v>303.5738223490225</v>
       </c>
       <c r="D97">
-        <v>8609.137653337209</v>
+        <v>8602.177822349022</v>
       </c>
       <c r="E97">
-        <v>1355.68</v>
+        <v>1450.704</v>
       </c>
       <c r="F97">
-        <v>9027.280000000001</v>
+        <v>9122.304</v>
       </c>
       <c r="G97">
         <v>823.7</v>
@@ -9241,28 +9241,28 @@
         <v>1573.55</v>
       </c>
       <c r="M97">
-        <v>684.2678240000001</v>
+        <v>691.4706432</v>
       </c>
       <c r="N97">
-        <v>889.2821759999998</v>
+        <v>882.0793567999999</v>
       </c>
       <c r="O97">
-        <v>133.3923264</v>
+        <v>132.31190352</v>
       </c>
       <c r="P97">
-        <v>755.8898495999998</v>
+        <v>749.7674532799999</v>
       </c>
       <c r="Q97">
-        <v>2301.0898496</v>
+        <v>2294.96745328</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7468200648484288</v>
+        <v>0.9205422383531418</v>
       </c>
       <c r="T97">
-        <v>9.136641475563302</v>
+        <v>11.40082376542593</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.299611270337913</v>
+        <v>2.275656986271894</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09867448953412561</v>
+        <v>0.09879947582582983</v>
       </c>
       <c r="C98">
-        <v>303.5738223490225</v>
+        <v>201.6012352557591</v>
       </c>
       <c r="D98">
-        <v>8602.177822349022</v>
+        <v>8595.229235255758</v>
       </c>
       <c r="E98">
-        <v>1450.704</v>
+        <v>1545.727999999999</v>
       </c>
       <c r="F98">
-        <v>9122.304</v>
+        <v>9217.328</v>
       </c>
       <c r="G98">
         <v>823.7</v>
@@ -9323,28 +9323,28 @@
         <v>1573.55</v>
       </c>
       <c r="M98">
-        <v>691.4706432</v>
+        <v>698.6734624000001</v>
       </c>
       <c r="N98">
-        <v>882.0793567999999</v>
+        <v>874.8765375999999</v>
       </c>
       <c r="O98">
-        <v>132.31190352</v>
+        <v>131.23148064</v>
       </c>
       <c r="P98">
-        <v>749.7674532799999</v>
+        <v>743.6450569599999</v>
       </c>
       <c r="Q98">
-        <v>2294.96745328</v>
+        <v>2288.84505696</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9205422383531394</v>
+        <v>1.210079194194327</v>
       </c>
       <c r="T98">
-        <v>11.4008237654259</v>
+        <v>15.17446091519694</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.275656986271894</v>
+        <v>2.252196604970122</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09879947582582983</v>
+        <v>0.09892446211753406</v>
       </c>
       <c r="C99">
-        <v>201.6012352557591</v>
+        <v>99.63986483194458</v>
       </c>
       <c r="D99">
-        <v>8595.229235255758</v>
+        <v>8588.291864831943</v>
       </c>
       <c r="E99">
-        <v>1545.727999999999</v>
+        <v>1640.751999999999</v>
       </c>
       <c r="F99">
-        <v>9217.328</v>
+        <v>9312.351999999999</v>
       </c>
       <c r="G99">
         <v>823.7</v>
@@ -9405,28 +9405,28 @@
         <v>1573.55</v>
       </c>
       <c r="M99">
-        <v>698.6734624000001</v>
+        <v>705.8762816</v>
       </c>
       <c r="N99">
-        <v>874.8765375999999</v>
+        <v>867.6737184</v>
       </c>
       <c r="O99">
-        <v>131.23148064</v>
+        <v>130.15105776</v>
       </c>
       <c r="P99">
-        <v>743.6450569599999</v>
+        <v>737.52266064</v>
       </c>
       <c r="Q99">
-        <v>2288.84505696</v>
+        <v>2282.72266064</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.210079194194327</v>
+        <v>1.789153105876701</v>
       </c>
       <c r="T99">
-        <v>15.17446091519694</v>
+        <v>22.72173521473901</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.252196604970122</v>
+        <v>2.229215006960223</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09892446211753406</v>
+        <v>0.09904944840923827</v>
       </c>
       <c r="C100">
-        <v>99.63986483194458</v>
+        <v>-2.310316060067635</v>
       </c>
       <c r="D100">
-        <v>8588.291864831943</v>
+        <v>8581.365683939932</v>
       </c>
       <c r="E100">
-        <v>1640.751999999999</v>
+        <v>1735.776</v>
       </c>
       <c r="F100">
-        <v>9312.351999999999</v>
+        <v>9407.376</v>
       </c>
       <c r="G100">
         <v>823.7</v>
@@ -9487,28 +9487,28 @@
         <v>1573.55</v>
       </c>
       <c r="M100">
-        <v>705.8762816</v>
+        <v>713.0791008000001</v>
       </c>
       <c r="N100">
-        <v>867.6737184</v>
+        <v>860.4708991999998</v>
       </c>
       <c r="O100">
-        <v>130.15105776</v>
+        <v>129.07063488</v>
       </c>
       <c r="P100">
-        <v>737.52266064</v>
+        <v>731.4002643199999</v>
       </c>
       <c r="Q100">
-        <v>2282.72266064</v>
+        <v>2276.60026432</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.789153105876701</v>
+        <v>3.526374840923823</v>
       </c>
       <c r="T100">
-        <v>22.72173521473901</v>
+        <v>45.36355811336521</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.229215006960223</v>
+        <v>2.206697683657594</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09904944840923827</v>
-      </c>
-      <c r="C101">
-        <v>-2.310316060067635</v>
-      </c>
-      <c r="D101">
-        <v>8581.365683939932</v>
-      </c>
-      <c r="E101">
-        <v>1735.776</v>
-      </c>
-      <c r="F101">
-        <v>9407.376</v>
-      </c>
-      <c r="G101">
-        <v>823.7</v>
-      </c>
-      <c r="H101">
-        <v>1830.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3118.75</v>
-      </c>
-      <c r="K101">
-        <v>1545.2</v>
-      </c>
-      <c r="L101">
-        <v>1573.55</v>
-      </c>
-      <c r="M101">
-        <v>713.0791008000001</v>
-      </c>
-      <c r="N101">
-        <v>860.4708991999998</v>
-      </c>
-      <c r="O101">
-        <v>129.07063488</v>
-      </c>
-      <c r="P101">
-        <v>731.4002643199999</v>
-      </c>
-      <c r="Q101">
-        <v>2276.60026432</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.526374840923823</v>
-      </c>
-      <c r="T101">
-        <v>45.36355811336521</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.06443</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.206697683657594</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
